--- a/kka-penilaian-saham.xlsx
+++ b/kka-penilaian-saham.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/persiapantubel/Desktop/claude/superpowers/kka-penilaian-saham/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{186D14FA-9DE6-5B46-8E71-582813103306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E307ACFE-F22B-5B4F-A620-34A05E8EE6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="16500" tabRatio="852" firstSheet="18" activeTab="34" xr2:uid="{9329EE89-472E-4BD7-BEEB-5D8C86697BEE}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16500" tabRatio="852" firstSheet="3" activeTab="10" xr2:uid="{9329EE89-472E-4BD7-BEEB-5D8C86697BEE}"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="3" r:id="rId1"/>
@@ -10829,7 +10829,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="669">
+  <cellXfs count="670">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -11653,6 +11653,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -33677,20 +33678,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="567" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="567"/>
-      <c r="C1" s="567"/>
-      <c r="D1" s="567"/>
-      <c r="E1" s="567"/>
+      <c r="A1" s="568" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="568"/>
+      <c r="C1" s="568"/>
+      <c r="D1" s="568"/>
+      <c r="E1" s="568"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="568"/>
-      <c r="B2" s="568"/>
-      <c r="C2" s="568"/>
-      <c r="D2" s="568"/>
-      <c r="E2" s="568"/>
+      <c r="A2" s="569"/>
+      <c r="B2" s="569"/>
+      <c r="C2" s="569"/>
+      <c r="D2" s="569"/>
+      <c r="E2" s="569"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="49" t="s">
@@ -34199,68 +34200,68 @@
       <c r="F1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="571" t="s">
+      <c r="A2" s="572" t="s">
         <v>2350</v>
       </c>
-      <c r="B2" s="571"/>
-      <c r="C2" s="571"/>
-      <c r="D2" s="571"/>
-      <c r="E2" s="571"/>
-      <c r="F2" s="571"/>
+      <c r="B2" s="572"/>
+      <c r="C2" s="572"/>
+      <c r="D2" s="572"/>
+      <c r="E2" s="572"/>
+      <c r="F2" s="572"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E3" s="121"/>
       <c r="F3" s="121"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="572" t="s">
+      <c r="A4" s="573" t="s">
         <v>2351</v>
       </c>
-      <c r="B4" s="572" t="s">
+      <c r="B4" s="573" t="s">
         <v>2352</v>
       </c>
-      <c r="C4" s="572" t="s">
+      <c r="C4" s="573" t="s">
         <v>2353</v>
       </c>
-      <c r="D4" s="573" t="s">
+      <c r="D4" s="574" t="s">
         <v>2354</v>
       </c>
-      <c r="E4" s="572" t="s">
+      <c r="E4" s="573" t="s">
         <v>2355</v>
       </c>
-      <c r="F4" s="572"/>
+      <c r="F4" s="573"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="572"/>
-      <c r="B5" s="572"/>
-      <c r="C5" s="572"/>
-      <c r="D5" s="574"/>
-      <c r="E5" s="572"/>
-      <c r="F5" s="572"/>
+      <c r="A5" s="573"/>
+      <c r="B5" s="573"/>
+      <c r="C5" s="573"/>
+      <c r="D5" s="575"/>
+      <c r="E5" s="573"/>
+      <c r="F5" s="573"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="572"/>
-      <c r="B6" s="572"/>
-      <c r="C6" s="572"/>
-      <c r="D6" s="575"/>
-      <c r="E6" s="572"/>
-      <c r="F6" s="572"/>
+      <c r="A6" s="573"/>
+      <c r="B6" s="573"/>
+      <c r="C6" s="573"/>
+      <c r="D6" s="576"/>
+      <c r="E6" s="573"/>
+      <c r="F6" s="573"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="572">
+      <c r="A7" s="573">
         <v>1</v>
       </c>
-      <c r="B7" s="576" t="s">
+      <c r="B7" s="577" t="s">
         <v>2860</v>
       </c>
-      <c r="C7" s="577" t="s">
+      <c r="C7" s="578" t="s">
         <v>2866</v>
       </c>
       <c r="D7" s="122"/>
-      <c r="E7" s="578" t="s">
+      <c r="E7" s="579" t="s">
         <v>2356</v>
       </c>
-      <c r="F7" s="573">
+      <c r="F7" s="574">
         <f>IF(E7="Ada",0,1)</f>
         <v>1</v>
       </c>
@@ -34284,12 +34285,12 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="572"/>
-      <c r="B8" s="576"/>
-      <c r="C8" s="577"/>
+      <c r="A8" s="573"/>
+      <c r="B8" s="577"/>
+      <c r="C8" s="578"/>
       <c r="D8" s="125"/>
-      <c r="E8" s="579"/>
-      <c r="F8" s="575"/>
+      <c r="E8" s="580"/>
+      <c r="F8" s="576"/>
       <c r="G8" s="124"/>
       <c r="H8" s="124" t="s">
         <v>2356</v>
@@ -34308,20 +34309,20 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="572">
+      <c r="A9" s="573">
         <v>2</v>
       </c>
-      <c r="B9" s="576" t="s">
+      <c r="B9" s="577" t="s">
         <v>2861</v>
       </c>
-      <c r="C9" s="577" t="s">
+      <c r="C9" s="578" t="s">
         <v>2865</v>
       </c>
       <c r="D9" s="122"/>
-      <c r="E9" s="578" t="s">
+      <c r="E9" s="579" t="s">
         <v>2361</v>
       </c>
-      <c r="F9" s="573">
+      <c r="F9" s="574">
         <f>IF(E9="Rendah",0,IF(E9="Sedang",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34343,29 +34344,29 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="572"/>
-      <c r="B10" s="576"/>
-      <c r="C10" s="577"/>
+      <c r="A10" s="573"/>
+      <c r="B10" s="577"/>
+      <c r="C10" s="578"/>
       <c r="D10" s="125"/>
-      <c r="E10" s="579"/>
-      <c r="F10" s="575"/>
+      <c r="E10" s="580"/>
+      <c r="F10" s="576"/>
       <c r="G10" s="124"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="572">
+      <c r="A11" s="573">
         <v>3</v>
       </c>
-      <c r="B11" s="576" t="s">
+      <c r="B11" s="577" t="s">
         <v>2862</v>
       </c>
-      <c r="C11" s="577" t="s">
+      <c r="C11" s="578" t="s">
         <v>2867</v>
       </c>
       <c r="D11" s="122"/>
-      <c r="E11" s="578" t="s">
+      <c r="E11" s="579" t="s">
         <v>2362</v>
       </c>
-      <c r="F11" s="573">
+      <c r="F11" s="574">
         <f>IF(E11="Rendah",0,IF(E11="Moderat",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34374,29 +34375,29 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="572"/>
-      <c r="B12" s="576"/>
-      <c r="C12" s="577"/>
+      <c r="A12" s="573"/>
+      <c r="B12" s="577"/>
+      <c r="C12" s="578"/>
       <c r="D12" s="125"/>
-      <c r="E12" s="579"/>
-      <c r="F12" s="575"/>
+      <c r="E12" s="580"/>
+      <c r="F12" s="576"/>
       <c r="G12" s="124"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="572">
+      <c r="A13" s="573">
         <v>4</v>
       </c>
-      <c r="B13" s="582" t="s">
+      <c r="B13" s="583" t="s">
         <v>2863</v>
       </c>
-      <c r="C13" s="576" t="s">
+      <c r="C13" s="577" t="s">
         <v>2868</v>
       </c>
       <c r="D13" s="126"/>
-      <c r="E13" s="578" t="s">
+      <c r="E13" s="579" t="s">
         <v>2363</v>
       </c>
-      <c r="F13" s="573">
+      <c r="F13" s="574">
         <f>IF(E13="Tidak Ada",0,IF(E13="Sebagian",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34405,29 +34406,29 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="572"/>
-      <c r="B14" s="582"/>
-      <c r="C14" s="576"/>
+      <c r="A14" s="573"/>
+      <c r="B14" s="583"/>
+      <c r="C14" s="577"/>
       <c r="D14" s="127"/>
-      <c r="E14" s="579"/>
-      <c r="F14" s="575"/>
+      <c r="E14" s="580"/>
+      <c r="F14" s="576"/>
       <c r="G14" s="124"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="572">
+      <c r="A15" s="573">
         <v>5</v>
       </c>
-      <c r="B15" s="576" t="s">
+      <c r="B15" s="577" t="s">
         <v>2864</v>
       </c>
-      <c r="C15" s="576" t="s">
+      <c r="C15" s="577" t="s">
         <v>2869</v>
       </c>
       <c r="D15" s="126"/>
-      <c r="E15" s="578" t="s">
+      <c r="E15" s="579" t="s">
         <v>2363</v>
       </c>
-      <c r="F15" s="573">
+      <c r="F15" s="574">
         <f>IF(E15="Tidak",0,IF(E15="Sebagian",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34436,21 +34437,21 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="572"/>
-      <c r="B16" s="576"/>
-      <c r="C16" s="576"/>
+      <c r="A16" s="573"/>
+      <c r="B16" s="577"/>
+      <c r="C16" s="577"/>
       <c r="D16" s="127"/>
-      <c r="E16" s="579"/>
-      <c r="F16" s="575"/>
+      <c r="E16" s="580"/>
+      <c r="F16" s="576"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="580" t="s">
+      <c r="A17" s="581" t="s">
         <v>2372</v>
       </c>
-      <c r="B17" s="581"/>
-      <c r="C17" s="581"/>
-      <c r="D17" s="581"/>
-      <c r="E17" s="581"/>
+      <c r="B17" s="582"/>
+      <c r="C17" s="582"/>
+      <c r="D17" s="582"/>
+      <c r="E17" s="582"/>
       <c r="F17" s="130">
         <f>SUM(F7:F16)</f>
         <v>3</v>
@@ -34491,7 +34492,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="556">
-        <f>IF(B31="Minoritas",5,7)</f>
+        <f>IF(B21="Minoritas",5,7)</f>
         <v>7</v>
       </c>
       <c r="B21" s="556" t="s">
@@ -34610,7 +34611,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="283"/>
-      <c r="B31" s="283"/>
+      <c r="B31" s="131"/>
       <c r="C31" s="283"/>
       <c r="D31" s="283"/>
       <c r="E31" s="283"/>
@@ -34697,68 +34698,68 @@
       <c r="G1" s="121"/>
     </row>
     <row r="2" spans="2:14" ht="19" x14ac:dyDescent="0.25">
-      <c r="B2" s="571" t="s">
+      <c r="B2" s="572" t="s">
         <v>2380</v>
       </c>
-      <c r="C2" s="571"/>
-      <c r="D2" s="571"/>
-      <c r="E2" s="571"/>
-      <c r="F2" s="571"/>
-      <c r="G2" s="571"/>
+      <c r="C2" s="572"/>
+      <c r="D2" s="572"/>
+      <c r="E2" s="572"/>
+      <c r="F2" s="572"/>
+      <c r="G2" s="572"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="F3" s="121"/>
       <c r="G3" s="121"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="572" t="s">
+      <c r="B4" s="573" t="s">
         <v>2351</v>
       </c>
-      <c r="C4" s="572" t="s">
+      <c r="C4" s="573" t="s">
         <v>2352</v>
       </c>
-      <c r="D4" s="572" t="s">
+      <c r="D4" s="573" t="s">
         <v>2381</v>
       </c>
-      <c r="E4" s="573" t="s">
+      <c r="E4" s="574" t="s">
         <v>2354</v>
       </c>
-      <c r="F4" s="572" t="s">
+      <c r="F4" s="573" t="s">
         <v>2382</v>
       </c>
-      <c r="G4" s="572"/>
+      <c r="G4" s="573"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="572"/>
-      <c r="C5" s="572"/>
-      <c r="D5" s="572"/>
-      <c r="E5" s="574"/>
-      <c r="F5" s="572"/>
-      <c r="G5" s="572"/>
+      <c r="B5" s="573"/>
+      <c r="C5" s="573"/>
+      <c r="D5" s="573"/>
+      <c r="E5" s="575"/>
+      <c r="F5" s="573"/>
+      <c r="G5" s="573"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="572"/>
-      <c r="C6" s="572"/>
-      <c r="D6" s="572"/>
-      <c r="E6" s="575"/>
-      <c r="F6" s="572"/>
-      <c r="G6" s="572"/>
+      <c r="B6" s="573"/>
+      <c r="C6" s="573"/>
+      <c r="D6" s="573"/>
+      <c r="E6" s="576"/>
+      <c r="F6" s="573"/>
+      <c r="G6" s="573"/>
     </row>
     <row r="7" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="572">
+      <c r="B7" s="573">
         <v>1</v>
       </c>
-      <c r="C7" s="582" t="s">
+      <c r="C7" s="583" t="s">
         <v>2383</v>
       </c>
-      <c r="D7" s="577" t="s">
+      <c r="D7" s="578" t="s">
         <v>2870</v>
       </c>
       <c r="E7" s="122"/>
-      <c r="F7" s="578" t="s">
+      <c r="F7" s="579" t="s">
         <v>2356</v>
       </c>
-      <c r="G7" s="572">
+      <c r="G7" s="573">
         <f>IF(F7="Ada",0,IF(F7="Terbatas",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34780,12 +34781,12 @@
       <c r="N7" s="124"/>
     </row>
     <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="572"/>
-      <c r="C8" s="582"/>
-      <c r="D8" s="577"/>
+      <c r="B8" s="573"/>
+      <c r="C8" s="583"/>
+      <c r="D8" s="578"/>
       <c r="E8" s="125"/>
-      <c r="F8" s="579"/>
-      <c r="G8" s="572"/>
+      <c r="F8" s="580"/>
+      <c r="G8" s="573"/>
       <c r="I8" s="123" t="s">
         <v>2387</v>
       </c>
@@ -34804,20 +34805,20 @@
       <c r="N8" s="124"/>
     </row>
     <row r="9" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="572">
+      <c r="B9" s="573">
         <v>2</v>
       </c>
-      <c r="C9" s="576" t="s">
+      <c r="C9" s="577" t="s">
         <v>2392</v>
       </c>
-      <c r="D9" s="577" t="s">
+      <c r="D9" s="578" t="s">
         <v>2871</v>
       </c>
       <c r="E9" s="122"/>
-      <c r="F9" s="578" t="s">
+      <c r="F9" s="579" t="s">
         <v>2393</v>
       </c>
-      <c r="G9" s="572">
+      <c r="G9" s="573">
         <f>IF(F9="Tidak Terbatas",0,IF(F9="Segmen Tertentu",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34839,12 +34840,12 @@
       <c r="N9" s="124"/>
     </row>
     <row r="10" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="572"/>
-      <c r="C10" s="576"/>
-      <c r="D10" s="577"/>
+      <c r="B10" s="573"/>
+      <c r="C10" s="577"/>
+      <c r="D10" s="578"/>
       <c r="E10" s="125"/>
-      <c r="F10" s="579"/>
-      <c r="G10" s="572"/>
+      <c r="F10" s="580"/>
+      <c r="G10" s="573"/>
       <c r="I10" s="124"/>
       <c r="J10" s="124"/>
       <c r="K10" s="124"/>
@@ -34853,20 +34854,20 @@
       <c r="N10" s="124"/>
     </row>
     <row r="11" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="572">
+      <c r="B11" s="573">
         <v>3</v>
       </c>
-      <c r="C11" s="582" t="s">
+      <c r="C11" s="583" t="s">
         <v>2396</v>
       </c>
-      <c r="D11" s="577" t="s">
+      <c r="D11" s="578" t="s">
         <v>2872</v>
       </c>
       <c r="E11" s="122"/>
-      <c r="F11" s="578" t="s">
+      <c r="F11" s="579" t="s">
         <v>2356</v>
       </c>
-      <c r="G11" s="572">
+      <c r="G11" s="573">
         <f>IF(F11="Ya",0,IF(F11="Kadang-kadang",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34888,12 +34889,12 @@
       <c r="N11" s="124"/>
     </row>
     <row r="12" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="572"/>
-      <c r="C12" s="582"/>
-      <c r="D12" s="577"/>
+      <c r="B12" s="573"/>
+      <c r="C12" s="583"/>
+      <c r="D12" s="578"/>
       <c r="E12" s="125"/>
-      <c r="F12" s="579"/>
-      <c r="G12" s="572"/>
+      <c r="F12" s="580"/>
+      <c r="G12" s="573"/>
       <c r="I12" s="123" t="s">
         <v>2390</v>
       </c>
@@ -34912,20 +34913,20 @@
       <c r="N12" s="124"/>
     </row>
     <row r="13" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="572">
+      <c r="B13" s="573">
         <v>4</v>
       </c>
-      <c r="C13" s="582" t="s">
+      <c r="C13" s="583" t="s">
         <v>2400</v>
       </c>
-      <c r="D13" s="576" t="s">
+      <c r="D13" s="577" t="s">
         <v>2873</v>
       </c>
       <c r="E13" s="126"/>
-      <c r="F13" s="578" t="s">
+      <c r="F13" s="579" t="s">
         <v>2394</v>
       </c>
-      <c r="G13" s="572">
+      <c r="G13" s="573">
         <f>IF(F13="Diatas",0,IF(F13="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34947,183 +34948,183 @@
       <c r="N13" s="124"/>
     </row>
     <row r="14" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="572"/>
-      <c r="C14" s="582"/>
-      <c r="D14" s="576"/>
+      <c r="B14" s="573"/>
+      <c r="C14" s="583"/>
+      <c r="D14" s="577"/>
       <c r="E14" s="127"/>
-      <c r="F14" s="579"/>
-      <c r="G14" s="572"/>
+      <c r="F14" s="580"/>
+      <c r="G14" s="573"/>
     </row>
     <row r="15" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="572">
+      <c r="B15" s="573">
         <v>5</v>
       </c>
-      <c r="C15" s="582" t="s">
+      <c r="C15" s="583" t="s">
         <v>2403</v>
       </c>
-      <c r="D15" s="576" t="s">
+      <c r="D15" s="577" t="s">
         <v>2874</v>
       </c>
       <c r="E15" s="126"/>
-      <c r="F15" s="578" t="s">
+      <c r="F15" s="579" t="s">
         <v>2395</v>
       </c>
-      <c r="G15" s="572">
+      <c r="G15" s="573">
         <f>IF(F15="Tidak, Meningkat",0,IF(F15="Sedang, Stabil",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="572"/>
-      <c r="C16" s="582"/>
-      <c r="D16" s="576"/>
+      <c r="B16" s="573"/>
+      <c r="C16" s="583"/>
+      <c r="D16" s="577"/>
       <c r="E16" s="127"/>
-      <c r="F16" s="579"/>
-      <c r="G16" s="572"/>
+      <c r="F16" s="580"/>
+      <c r="G16" s="573"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="572">
+      <c r="B17" s="573">
         <v>6</v>
       </c>
-      <c r="C17" s="582" t="s">
+      <c r="C17" s="583" t="s">
         <v>2404</v>
       </c>
-      <c r="D17" s="576" t="s">
+      <c r="D17" s="577" t="s">
         <v>2875</v>
       </c>
       <c r="E17" s="126"/>
-      <c r="F17" s="578" t="s">
+      <c r="F17" s="579" t="s">
         <v>2385</v>
       </c>
-      <c r="G17" s="572">
+      <c r="G17" s="573">
         <f>IF(F17="Dibawah",0,IF(F17="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="572"/>
-      <c r="C18" s="582"/>
-      <c r="D18" s="576"/>
+      <c r="B18" s="573"/>
+      <c r="C18" s="583"/>
+      <c r="D18" s="577"/>
       <c r="E18" s="127"/>
-      <c r="F18" s="579"/>
-      <c r="G18" s="572"/>
+      <c r="F18" s="580"/>
+      <c r="G18" s="573"/>
     </row>
     <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="572">
+      <c r="B19" s="573">
         <v>7</v>
       </c>
-      <c r="C19" s="582" t="s">
+      <c r="C19" s="583" t="s">
         <v>2405</v>
       </c>
-      <c r="D19" s="576" t="s">
+      <c r="D19" s="577" t="s">
         <v>2876</v>
       </c>
       <c r="E19" s="126"/>
-      <c r="F19" s="578" t="s">
+      <c r="F19" s="579" t="s">
         <v>2394</v>
       </c>
-      <c r="G19" s="572">
+      <c r="G19" s="573">
         <f>IF(F19="Diatas",0,IF(F19="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="572"/>
-      <c r="C20" s="582"/>
-      <c r="D20" s="576"/>
+      <c r="B20" s="573"/>
+      <c r="C20" s="583"/>
+      <c r="D20" s="577"/>
       <c r="E20" s="127"/>
-      <c r="F20" s="579"/>
-      <c r="G20" s="572"/>
+      <c r="F20" s="580"/>
+      <c r="G20" s="573"/>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="572">
+      <c r="B21" s="573">
         <v>8</v>
       </c>
-      <c r="C21" s="576" t="s">
+      <c r="C21" s="577" t="s">
         <v>2406</v>
       </c>
-      <c r="D21" s="576" t="s">
+      <c r="D21" s="577" t="s">
         <v>2877</v>
       </c>
       <c r="E21" s="126"/>
-      <c r="F21" s="578" t="s">
+      <c r="F21" s="579" t="s">
         <v>2401</v>
       </c>
-      <c r="G21" s="572">
+      <c r="G21" s="573">
         <f>IF(F21="Lebih Besar",0,IF(F21="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="572"/>
-      <c r="C22" s="576"/>
-      <c r="D22" s="576"/>
+      <c r="B22" s="573"/>
+      <c r="C22" s="577"/>
+      <c r="D22" s="577"/>
       <c r="E22" s="127"/>
-      <c r="F22" s="579"/>
-      <c r="G22" s="572"/>
+      <c r="F22" s="580"/>
+      <c r="G22" s="573"/>
     </row>
     <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="572">
+      <c r="B23" s="573">
         <v>9</v>
       </c>
-      <c r="C23" s="576" t="s">
+      <c r="C23" s="577" t="s">
         <v>2407</v>
       </c>
-      <c r="D23" s="576" t="s">
+      <c r="D23" s="577" t="s">
         <v>2878</v>
       </c>
       <c r="E23" s="126"/>
-      <c r="F23" s="578" t="s">
+      <c r="F23" s="579" t="s">
         <v>2402</v>
       </c>
-      <c r="G23" s="572">
+      <c r="G23" s="573">
         <f>IF(F23="Meningkat",0,IF(F23="Seperti Saat Ini",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="572"/>
-      <c r="C24" s="576"/>
-      <c r="D24" s="576"/>
+      <c r="B24" s="573"/>
+      <c r="C24" s="577"/>
+      <c r="D24" s="577"/>
       <c r="E24" s="127"/>
-      <c r="F24" s="579"/>
-      <c r="G24" s="572"/>
+      <c r="F24" s="580"/>
+      <c r="G24" s="573"/>
     </row>
     <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="572">
+      <c r="B25" s="573">
         <v>10</v>
       </c>
-      <c r="C25" s="582" t="s">
+      <c r="C25" s="583" t="s">
         <v>2408</v>
       </c>
-      <c r="D25" s="583" t="s">
+      <c r="D25" s="584" t="s">
         <v>2879</v>
       </c>
       <c r="E25" s="128"/>
-      <c r="F25" s="578" t="s">
+      <c r="F25" s="579" t="s">
         <v>2360</v>
       </c>
-      <c r="G25" s="572">
+      <c r="G25" s="573">
         <f>IF(F25="Ya",0,IF(F25="Seperti Saat Ini",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="572"/>
-      <c r="C26" s="582"/>
-      <c r="D26" s="583"/>
+      <c r="B26" s="573"/>
+      <c r="C26" s="583"/>
+      <c r="D26" s="584"/>
       <c r="E26" s="129"/>
-      <c r="F26" s="579"/>
-      <c r="G26" s="572"/>
+      <c r="F26" s="580"/>
+      <c r="G26" s="573"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="584" t="s">
+      <c r="B27" s="585" t="s">
         <v>2372</v>
       </c>
-      <c r="C27" s="584"/>
-      <c r="D27" s="584"/>
-      <c r="E27" s="584"/>
-      <c r="F27" s="584"/>
+      <c r="C27" s="585"/>
+      <c r="D27" s="585"/>
+      <c r="E27" s="585"/>
+      <c r="F27" s="585"/>
       <c r="G27" s="130">
         <f>SUM(G7:G26)</f>
         <v>10</v>
@@ -35635,10 +35636,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="N2" s="569" t="s">
+      <c r="N2" s="570" t="s">
         <v>2414</v>
       </c>
-      <c r="O2" s="569"/>
+      <c r="O2" s="570"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.2">
       <c r="N3" s="501"/>
@@ -35719,63 +35720,63 @@
       <c r="C11" s="489" t="s">
         <v>2417</v>
       </c>
-      <c r="D11" s="585">
+      <c r="D11" s="586">
         <f>'INCOME STATEMENT'!E35</f>
         <v>4994138866</v>
       </c>
-      <c r="E11" s="586"/>
+      <c r="E11" s="587"/>
       <c r="F11" s="490"/>
       <c r="H11" s="489" t="s">
         <v>2417</v>
       </c>
-      <c r="I11" s="588"/>
-      <c r="J11" s="589"/>
+      <c r="I11" s="589"/>
+      <c r="J11" s="590"/>
       <c r="L11" s="489" t="s">
         <v>2417</v>
       </c>
-      <c r="M11" s="587">
+      <c r="M11" s="588">
         <f>'INCOME STATEMENT'!F35</f>
         <v>5805826735</v>
       </c>
-      <c r="N11" s="590"/>
+      <c r="N11" s="591"/>
       <c r="Q11" t="s">
         <v>2417</v>
       </c>
-      <c r="R11" s="587">
+      <c r="R11" s="588">
         <v>135354171907</v>
       </c>
-      <c r="S11" s="587"/>
+      <c r="S11" s="588"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C12" s="489" t="s">
         <v>2418</v>
       </c>
-      <c r="D12" s="585">
+      <c r="D12" s="586">
         <f>'BALANCE SHEET'!E49</f>
         <v>23663464279</v>
       </c>
-      <c r="E12" s="586"/>
+      <c r="E12" s="587"/>
       <c r="F12" s="490"/>
       <c r="H12" s="489" t="s">
         <v>2418</v>
       </c>
-      <c r="I12" s="588"/>
-      <c r="J12" s="589"/>
+      <c r="I12" s="589"/>
+      <c r="J12" s="590"/>
       <c r="L12" s="489" t="s">
         <v>2418</v>
       </c>
-      <c r="M12" s="587">
+      <c r="M12" s="588">
         <f>'BALANCE SHEET'!F49</f>
         <v>29366482204</v>
       </c>
-      <c r="N12" s="590"/>
+      <c r="N12" s="591"/>
       <c r="Q12" t="s">
         <v>2418</v>
       </c>
-      <c r="R12" s="587">
+      <c r="R12" s="588">
         <v>635570945239</v>
       </c>
-      <c r="S12" s="587"/>
+      <c r="S12" s="588"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C13" s="489" t="s">
@@ -35879,26 +35880,26 @@
       <c r="J2" s="486"/>
       <c r="K2" s="486"/>
       <c r="L2" s="487"/>
-      <c r="M2" s="596" t="s">
+      <c r="M2" s="597" t="s">
         <v>2421</v>
       </c>
-      <c r="N2" s="597"/>
-      <c r="O2" s="597"/>
-      <c r="P2" s="597"/>
-      <c r="Q2" s="597"/>
-      <c r="R2" s="597"/>
-      <c r="S2" s="597"/>
-      <c r="T2" s="598"/>
-      <c r="U2" s="596" t="s">
+      <c r="N2" s="598"/>
+      <c r="O2" s="598"/>
+      <c r="P2" s="598"/>
+      <c r="Q2" s="598"/>
+      <c r="R2" s="598"/>
+      <c r="S2" s="598"/>
+      <c r="T2" s="599"/>
+      <c r="U2" s="597" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="597"/>
-      <c r="W2" s="597"/>
-      <c r="X2" s="597"/>
-      <c r="Y2" s="597"/>
-      <c r="Z2" s="597"/>
-      <c r="AA2" s="597"/>
-      <c r="AB2" s="598"/>
+      <c r="V2" s="598"/>
+      <c r="W2" s="598"/>
+      <c r="X2" s="598"/>
+      <c r="Y2" s="598"/>
+      <c r="Z2" s="598"/>
+      <c r="AA2" s="598"/>
+      <c r="AB2" s="599"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B3" s="480"/>
@@ -36641,41 +36642,41 @@
       <c r="G59" s="518" t="s">
         <v>2417</v>
       </c>
-      <c r="H59" s="591">
+      <c r="H59" s="592">
         <f>TL!D11</f>
         <v>4994138866</v>
       </c>
-      <c r="I59" s="592"/>
+      <c r="I59" s="593"/>
       <c r="J59" s="510"/>
       <c r="K59" s="507"/>
       <c r="L59" s="518" t="str">
         <f>TL!H11</f>
         <v>Net Profit</v>
       </c>
-      <c r="M59" s="594">
+      <c r="M59" s="595">
         <f>TL!I11</f>
         <v>0</v>
       </c>
-      <c r="N59" s="595"/>
+      <c r="N59" s="596"/>
       <c r="O59" s="507"/>
       <c r="P59" s="518" t="s">
         <v>2417</v>
       </c>
-      <c r="Q59" s="591">
+      <c r="Q59" s="592">
         <f>TL!M11</f>
         <v>5805826735</v>
       </c>
-      <c r="R59" s="593"/>
+      <c r="R59" s="594"/>
       <c r="S59" s="507"/>
       <c r="T59" s="507"/>
       <c r="U59" s="507" t="s">
         <v>2417</v>
       </c>
-      <c r="V59" s="591">
+      <c r="V59" s="592">
         <f>TL!R11</f>
         <v>135354171907</v>
       </c>
-      <c r="W59" s="591"/>
+      <c r="W59" s="592"/>
       <c r="X59" s="507"/>
       <c r="Y59" s="507"/>
       <c r="Z59" s="507"/>
@@ -36691,41 +36692,41 @@
       <c r="G60" s="518" t="s">
         <v>2418</v>
       </c>
-      <c r="H60" s="591">
+      <c r="H60" s="592">
         <f>TL!D12</f>
         <v>23663464279</v>
       </c>
-      <c r="I60" s="592"/>
+      <c r="I60" s="593"/>
       <c r="J60" s="510"/>
       <c r="K60" s="507"/>
       <c r="L60" s="518" t="str">
         <f>TL!H12</f>
         <v>Ekuitas</v>
       </c>
-      <c r="M60" s="594">
+      <c r="M60" s="595">
         <f>TL!I12</f>
         <v>0</v>
       </c>
-      <c r="N60" s="595"/>
+      <c r="N60" s="596"/>
       <c r="O60" s="507"/>
       <c r="P60" s="518" t="s">
         <v>2418</v>
       </c>
-      <c r="Q60" s="591">
+      <c r="Q60" s="592">
         <f>TL!M12</f>
         <v>29366482204</v>
       </c>
-      <c r="R60" s="593"/>
+      <c r="R60" s="594"/>
       <c r="S60" s="507"/>
       <c r="T60" s="507"/>
       <c r="U60" s="507" t="s">
         <v>2418</v>
       </c>
-      <c r="V60" s="591">
+      <c r="V60" s="592">
         <f>TL!R12</f>
         <v>635570945239</v>
       </c>
-      <c r="W60" s="591"/>
+      <c r="W60" s="592"/>
       <c r="X60" s="507"/>
       <c r="Y60" s="507"/>
       <c r="Z60" s="507"/>
@@ -36952,12 +36953,12 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="570" t="s">
+      <c r="H3" s="571" t="s">
         <v>2220</v>
       </c>
-      <c r="I3" s="570"/>
-      <c r="J3" s="570"/>
-      <c r="K3" s="570"/>
+      <c r="I3" s="571"/>
+      <c r="J3" s="571"/>
+      <c r="K3" s="571"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
     </row>
@@ -39148,15 +39149,15 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E4" s="599" t="s">
+      <c r="E4" s="600" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="599"/>
-      <c r="G4" s="599"/>
-      <c r="H4" s="599"/>
-      <c r="I4" s="599"/>
-      <c r="J4" s="599"/>
-      <c r="K4" s="599"/>
+      <c r="F4" s="600"/>
+      <c r="G4" s="600"/>
+      <c r="H4" s="600"/>
+      <c r="I4" s="600"/>
+      <c r="J4" s="600"/>
+      <c r="K4" s="600"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
@@ -39476,11 +39477,11 @@
       </c>
     </row>
     <row r="10" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="G10" s="600" t="s">
+      <c r="G10" s="601" t="s">
         <v>2439</v>
       </c>
-      <c r="H10" s="601"/>
-      <c r="I10" s="602"/>
+      <c r="H10" s="602"/>
+      <c r="I10" s="603"/>
       <c r="J10" s="232">
         <f>SUM(J3:J9)</f>
         <v>0</v>
@@ -53024,17 +53025,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="603" t="s">
+      <c r="A1" s="604" t="s">
         <v>2440</v>
       </c>
-      <c r="B1" s="603"/>
+      <c r="B1" s="604"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="604" t="str">
+      <c r="A2" s="605" t="str">
         <f>"Asumsi kondisi "&amp;HOME!B4&amp;" pada saat tanggal Penilaian ("&amp;TEXT(HOME!B10,"dd/mm/yyyy")&amp;")"</f>
         <v>Asumsi kondisi PT RAJA VOLTAMA ELEKTRIK pada saat tanggal Penilaian (31/12/2021)</v>
       </c>
-      <c r="B2" s="604"/>
+      <c r="B2" s="605"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="208" t="s">
@@ -59990,18 +59991,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="569" t="s">
+      <c r="A1" s="570" t="s">
         <v>2553</v>
       </c>
-      <c r="B1" s="569"/>
-      <c r="C1" s="569"/>
-      <c r="D1" s="569"/>
-      <c r="E1" s="569"/>
-      <c r="F1" s="569"/>
-      <c r="G1" s="569"/>
-      <c r="H1" s="569"/>
-      <c r="I1" s="569"/>
-      <c r="J1" s="569"/>
+      <c r="B1" s="570"/>
+      <c r="C1" s="570"/>
+      <c r="D1" s="570"/>
+      <c r="E1" s="570"/>
+      <c r="F1" s="570"/>
+      <c r="G1" s="570"/>
+      <c r="H1" s="570"/>
+      <c r="I1" s="570"/>
+      <c r="J1" s="570"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
@@ -61024,12 +61025,12 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="606" t="s">
+      <c r="A15" s="607" t="s">
         <v>2569</v>
       </c>
-      <c r="B15" s="606"/>
-      <c r="C15" s="606"/>
-      <c r="D15" s="606"/>
+      <c r="B15" s="607"/>
+      <c r="C15" s="607"/>
+      <c r="D15" s="607"/>
       <c r="E15" s="45">
         <f>E14*(1+((1-'INCOME STATEMENT'!B33)*(D14/C14)))</f>
         <v>0.98588588588588588</v>
@@ -61101,12 +61102,12 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="605" t="s">
+      <c r="A22" s="606" t="s">
         <v>2576</v>
       </c>
-      <c r="B22" s="605"/>
-      <c r="C22" s="605"/>
-      <c r="D22" s="605"/>
+      <c r="B22" s="606"/>
+      <c r="C22" s="606"/>
+      <c r="D22" s="606"/>
       <c r="E22" s="197">
         <v>0.1031</v>
       </c>
@@ -61199,12 +61200,12 @@
       <c r="A2" t="s">
         <v>2219</v>
       </c>
-      <c r="H2" s="569" t="s">
+      <c r="H2" s="570" t="s">
         <v>2220</v>
       </c>
-      <c r="I2" s="569"/>
-      <c r="J2" s="569"/>
-      <c r="K2" s="569"/>
+      <c r="I2" s="570"/>
+      <c r="J2" s="570"/>
+      <c r="K2" s="570"/>
       <c r="O2" s="163"/>
       <c r="P2" s="179" t="s">
         <v>2843</v>
@@ -61239,13 +61240,16 @@
         <v>2021</v>
       </c>
       <c r="H4" s="88">
+        <f>D4</f>
+        <v>2019</v>
+      </c>
+      <c r="I4" s="88">
+        <f>E4</f>
+        <v>2020</v>
+      </c>
+      <c r="J4" s="88">
+        <f>F4</f>
         <v>2021</v>
-      </c>
-      <c r="I4" s="88">
-        <v>2022</v>
-      </c>
-      <c r="J4" s="88">
-        <v>2023</v>
       </c>
       <c r="K4" s="88" t="s">
         <v>2222</v>
@@ -61319,11 +61323,11 @@
         <v>6635142218</v>
       </c>
       <c r="H8" s="90">
-        <f t="shared" ref="H8:J14" si="0">D8/D$27</f>
+        <f>D8/D$27</f>
         <v>0.29929419192407447</v>
       </c>
       <c r="I8" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H8:J14" si="0">E8/E$27</f>
         <v>0.11125799079079146</v>
       </c>
       <c r="J8" s="90">
@@ -61368,11 +61372,11 @@
         <v>9652447673</v>
       </c>
       <c r="H9" s="90">
-        <f t="shared" si="0"/>
+        <f>D9/D$27</f>
         <v>1.292793387268177E-2</v>
       </c>
       <c r="I9" s="90">
-        <f t="shared" si="0"/>
+        <f>E9/E$27</f>
         <v>0.17428840281020594</v>
       </c>
       <c r="J9" s="90">
@@ -61470,7 +61474,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="90">
-        <f t="shared" si="0"/>
+        <f>E11/E$27</f>
         <v>0</v>
       </c>
       <c r="J11" s="90">
@@ -61757,11 +61761,11 @@
         <v>6989653544</v>
       </c>
       <c r="H20" s="90">
-        <f t="shared" ref="H20:J21" si="6">D20/D$27</f>
+        <f>D20/D$27</f>
         <v>0.25374026841759106</v>
       </c>
       <c r="I20" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H20:J21" si="6">E20/E$27</f>
         <v>0.21944543986714599</v>
       </c>
       <c r="J20" s="90">
@@ -62268,7 +62272,7 @@
         <v>0.12745334015507079</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="11"/>
+        <f>E34/E$51</f>
         <v>0.11232920287269216</v>
       </c>
       <c r="J34" s="90">
@@ -62961,52 +62965,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="607" t="s">
+      <c r="A2" s="608" t="s">
         <v>2582</v>
       </c>
-      <c r="B2" s="607"/>
-      <c r="C2" s="607"/>
-      <c r="D2" s="607"/>
-      <c r="E2" s="607"/>
-      <c r="F2" s="607"/>
-      <c r="G2" s="607"/>
-      <c r="H2" s="607"/>
-      <c r="I2" s="607"/>
-      <c r="J2" s="607"/>
+      <c r="B2" s="608"/>
+      <c r="C2" s="608"/>
+      <c r="D2" s="608"/>
+      <c r="E2" s="608"/>
+      <c r="F2" s="608"/>
+      <c r="G2" s="608"/>
+      <c r="H2" s="608"/>
+      <c r="I2" s="608"/>
+      <c r="J2" s="608"/>
     </row>
     <row r="3" spans="1:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="608" t="str">
+      <c r="A4" s="609" t="str">
         <f>HOME!B4</f>
         <v>PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="B4" s="608"/>
-      <c r="C4" s="608"/>
-      <c r="D4" s="608"/>
-      <c r="E4" s="608"/>
-      <c r="F4" s="608"/>
-      <c r="G4" s="608"/>
-      <c r="H4" s="608"/>
-      <c r="I4" s="608"/>
-      <c r="J4" s="608"/>
+      <c r="B4" s="609"/>
+      <c r="C4" s="609"/>
+      <c r="D4" s="609"/>
+      <c r="E4" s="609"/>
+      <c r="F4" s="609"/>
+      <c r="G4" s="609"/>
+      <c r="H4" s="609"/>
+      <c r="I4" s="609"/>
+      <c r="J4" s="609"/>
     </row>
     <row r="5" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="609" t="str">
+      <c r="A6" s="610" t="str">
         <f>"DATA PENJUALAN "&amp;HOME!B4</f>
         <v>DATA PENJUALAN PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="B6" s="609"/>
-      <c r="C6" s="609"/>
-      <c r="D6" s="609"/>
-      <c r="E6" s="609"/>
-      <c r="G6" s="610" t="str">
+      <c r="B6" s="610"/>
+      <c r="C6" s="610"/>
+      <c r="D6" s="610"/>
+      <c r="E6" s="610"/>
+      <c r="G6" s="611" t="str">
         <f>"GROWTH SALES AND NET INCOME "&amp;HOME!B4</f>
         <v>GROWTH SALES AND NET INCOME PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="H6" s="610"/>
-      <c r="I6" s="610"/>
-      <c r="J6" s="610"/>
+      <c r="H6" s="611"/>
+      <c r="I6" s="611"/>
+      <c r="J6" s="611"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
@@ -63355,35 +63359,35 @@
       <c r="O32" s="56"/>
     </row>
     <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="608" t="s">
+      <c r="A36" s="609" t="s">
         <v>2593</v>
       </c>
-      <c r="B36" s="608"/>
-      <c r="C36" s="608"/>
-      <c r="D36" s="608"/>
-      <c r="E36" s="608"/>
-      <c r="F36" s="608"/>
-      <c r="G36" s="608"/>
-      <c r="H36" s="608"/>
-      <c r="I36" s="608"/>
-      <c r="J36" s="608"/>
+      <c r="B36" s="609"/>
+      <c r="C36" s="609"/>
+      <c r="D36" s="609"/>
+      <c r="E36" s="609"/>
+      <c r="F36" s="609"/>
+      <c r="G36" s="609"/>
+      <c r="H36" s="609"/>
+      <c r="I36" s="609"/>
+      <c r="J36" s="609"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="609" t="str">
+      <c r="A38" s="610" t="str">
         <f>"DATA PENJUALAN/PENDAPATAN INDUSTRI"</f>
         <v>DATA PENJUALAN/PENDAPATAN INDUSTRI</v>
       </c>
-      <c r="B38" s="609"/>
-      <c r="C38" s="609"/>
-      <c r="D38" s="609"/>
-      <c r="E38" s="609"/>
-      <c r="G38" s="610" t="str">
+      <c r="B38" s="610"/>
+      <c r="C38" s="610"/>
+      <c r="D38" s="610"/>
+      <c r="E38" s="610"/>
+      <c r="G38" s="611" t="str">
         <f>"GROWTH INDUSTRI "</f>
         <v xml:space="preserve">GROWTH INDUSTRI </v>
       </c>
-      <c r="H38" s="610"/>
-      <c r="I38" s="610"/>
-      <c r="J38" s="610"/>
+      <c r="H38" s="611"/>
+      <c r="I38" s="611"/>
+      <c r="J38" s="611"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="50" t="s">
@@ -63470,49 +63474,49 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="19" x14ac:dyDescent="0.25">
-      <c r="A58" s="607" t="str">
+      <c r="A58" s="608" t="str">
         <f>A2</f>
         <v>GROWTH</v>
       </c>
-      <c r="B58" s="607"/>
-      <c r="C58" s="607"/>
-      <c r="D58" s="607"/>
-      <c r="E58" s="607"/>
-      <c r="F58" s="607"/>
-      <c r="G58" s="607"/>
-      <c r="H58" s="607"/>
-      <c r="I58" s="607"/>
-      <c r="J58" s="607"/>
+      <c r="B58" s="608"/>
+      <c r="C58" s="608"/>
+      <c r="D58" s="608"/>
+      <c r="E58" s="608"/>
+      <c r="F58" s="608"/>
+      <c r="G58" s="608"/>
+      <c r="H58" s="608"/>
+      <c r="I58" s="608"/>
+      <c r="J58" s="608"/>
     </row>
     <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="608" t="str">
+      <c r="A60" s="609" t="str">
         <f>"PERBANDINGAN GROWTH INDUSTRI DENGAN "&amp;A4</f>
         <v>PERBANDINGAN GROWTH INDUSTRI DENGAN PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="B60" s="608"/>
-      <c r="C60" s="608"/>
-      <c r="D60" s="608"/>
-      <c r="E60" s="608"/>
-      <c r="F60" s="608"/>
-      <c r="G60" s="608"/>
-      <c r="H60" s="608"/>
-      <c r="I60" s="608"/>
-      <c r="J60" s="608"/>
+      <c r="B60" s="609"/>
+      <c r="C60" s="609"/>
+      <c r="D60" s="609"/>
+      <c r="E60" s="609"/>
+      <c r="F60" s="609"/>
+      <c r="G60" s="609"/>
+      <c r="H60" s="609"/>
+      <c r="I60" s="609"/>
+      <c r="J60" s="609"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" s="609" t="s">
+      <c r="A62" s="610" t="s">
         <v>2595</v>
       </c>
-      <c r="B62" s="609"/>
-      <c r="C62" s="609"/>
-      <c r="D62" s="609"/>
-      <c r="E62" s="609"/>
-      <c r="G62" s="610" t="s">
+      <c r="B62" s="610"/>
+      <c r="C62" s="610"/>
+      <c r="D62" s="610"/>
+      <c r="E62" s="610"/>
+      <c r="G62" s="611" t="s">
         <v>2596</v>
       </c>
-      <c r="H62" s="610"/>
-      <c r="I62" s="610"/>
-      <c r="J62" s="610"/>
+      <c r="H62" s="611"/>
+      <c r="I62" s="611"/>
+      <c r="J62" s="611"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="50" t="s">
@@ -63623,21 +63627,21 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" s="609" t="str">
+      <c r="A66" s="610" t="str">
         <f>"DATA PENJUALAN/PENDAPATAN INDUSTRI"</f>
         <v>DATA PENJUALAN/PENDAPATAN INDUSTRI</v>
       </c>
-      <c r="B66" s="609"/>
-      <c r="C66" s="609"/>
-      <c r="D66" s="609"/>
-      <c r="E66" s="609"/>
-      <c r="G66" s="610" t="str">
+      <c r="B66" s="610"/>
+      <c r="C66" s="610"/>
+      <c r="D66" s="610"/>
+      <c r="E66" s="610"/>
+      <c r="G66" s="611" t="str">
         <f>"GROWTH INDUSTRI "</f>
         <v xml:space="preserve">GROWTH INDUSTRI </v>
       </c>
-      <c r="H66" s="610"/>
-      <c r="I66" s="610"/>
-      <c r="J66" s="610"/>
+      <c r="H66" s="611"/>
+      <c r="I66" s="611"/>
+      <c r="J66" s="611"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="50" t="s">
@@ -63831,29 +63835,29 @@
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B2" s="614" t="s">
+      <c r="B2" s="615" t="s">
         <v>2602</v>
       </c>
-      <c r="C2" s="617" t="s">
+      <c r="C2" s="618" t="s">
         <v>2603</v>
       </c>
-      <c r="D2" s="617"/>
-      <c r="E2" s="617"/>
-      <c r="F2" s="618"/>
-      <c r="G2" s="616" t="s">
+      <c r="D2" s="618"/>
+      <c r="E2" s="618"/>
+      <c r="F2" s="619"/>
+      <c r="G2" s="617" t="s">
         <v>2604</v>
       </c>
-      <c r="H2" s="617"/>
-      <c r="I2" s="617"/>
-      <c r="J2" s="618"/>
-      <c r="K2" s="616" t="s">
+      <c r="H2" s="618"/>
+      <c r="I2" s="618"/>
+      <c r="J2" s="619"/>
+      <c r="K2" s="617" t="s">
         <v>2605</v>
       </c>
-      <c r="L2" s="617"/>
-      <c r="M2" s="618"/>
+      <c r="L2" s="618"/>
+      <c r="M2" s="619"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="615"/>
+      <c r="B3" s="616"/>
       <c r="C3" s="279" t="e">
         <f>'PASAR KESEBANDINGAN'!#REF!</f>
         <v>#REF!</v>
@@ -64488,15 +64492,15 @@
       <c r="B24" s="276" t="s">
         <v>2623</v>
       </c>
-      <c r="C24" s="611" t="s">
+      <c r="C24" s="612" t="s">
         <v>2624</v>
       </c>
-      <c r="D24" s="612"/>
-      <c r="E24" s="613"/>
-      <c r="F24" s="611" t="s">
+      <c r="D24" s="613"/>
+      <c r="E24" s="614"/>
+      <c r="F24" s="612" t="s">
         <v>2625</v>
       </c>
-      <c r="G24" s="613"/>
+      <c r="G24" s="614"/>
       <c r="H24" s="277" t="s">
         <v>2626</v>
       </c>
@@ -64803,28 +64807,28 @@
       <c r="G5" s="227"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="619" t="s">
+      <c r="A6" s="620" t="s">
         <v>2351</v>
       </c>
-      <c r="B6" s="621" t="s">
+      <c r="B6" s="622" t="s">
         <v>2643</v>
       </c>
-      <c r="C6" s="621"/>
-      <c r="D6" s="621"/>
-      <c r="E6" s="621"/>
-      <c r="F6" s="619" t="s">
+      <c r="C6" s="622"/>
+      <c r="D6" s="622"/>
+      <c r="E6" s="622"/>
+      <c r="F6" s="620" t="s">
         <v>2606</v>
       </c>
-      <c r="G6" s="619" t="s">
+      <c r="G6" s="620" t="s">
         <v>2605</v>
       </c>
-      <c r="J6" s="569"/>
-      <c r="K6" s="569"/>
-      <c r="L6" s="569"/>
-      <c r="M6" s="569"/>
+      <c r="J6" s="570"/>
+      <c r="K6" s="570"/>
+      <c r="L6" s="570"/>
+      <c r="M6" s="570"/>
     </row>
     <row r="7" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="620"/>
+      <c r="A7" s="621"/>
       <c r="B7" s="336" t="s">
         <v>2644</v>
       </c>
@@ -64837,8 +64841,8 @@
       <c r="E7" s="336" t="s">
         <v>2604</v>
       </c>
-      <c r="F7" s="620"/>
-      <c r="G7" s="620"/>
+      <c r="F7" s="621"/>
+      <c r="G7" s="621"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="337">
@@ -65121,12 +65125,12 @@
     <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="341"/>
       <c r="B31" s="320"/>
-      <c r="C31" s="622" t="s">
+      <c r="C31" s="623" t="s">
         <v>2372</v>
       </c>
-      <c r="D31" s="623"/>
-      <c r="E31" s="623"/>
-      <c r="F31" s="624"/>
+      <c r="D31" s="624"/>
+      <c r="E31" s="624"/>
+      <c r="F31" s="625"/>
       <c r="G31" s="342">
         <f>SUM(G27:G30)</f>
         <v>0</v>
@@ -65205,12 +65209,12 @@
     <row r="36" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="341"/>
       <c r="B36" s="320"/>
-      <c r="C36" s="622" t="s">
+      <c r="C36" s="623" t="s">
         <v>2372</v>
       </c>
-      <c r="D36" s="623"/>
-      <c r="E36" s="623"/>
-      <c r="F36" s="624"/>
+      <c r="D36" s="624"/>
+      <c r="E36" s="624"/>
+      <c r="F36" s="625"/>
       <c r="G36" s="342">
         <f>SUM(G32:G35)</f>
         <v>0</v>
@@ -65497,12 +65501,12 @@
     <row r="60" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="341"/>
       <c r="B60" s="320"/>
-      <c r="C60" s="622" t="s">
+      <c r="C60" s="623" t="s">
         <v>2372</v>
       </c>
-      <c r="D60" s="623"/>
-      <c r="E60" s="623"/>
-      <c r="F60" s="624"/>
+      <c r="D60" s="624"/>
+      <c r="E60" s="624"/>
+      <c r="F60" s="625"/>
       <c r="G60" s="342">
         <f>SUM(G56:G59)</f>
         <v>0</v>
@@ -65581,12 +65585,12 @@
     <row r="65" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="341"/>
       <c r="B65" s="320"/>
-      <c r="C65" s="622" t="s">
+      <c r="C65" s="623" t="s">
         <v>2372</v>
       </c>
-      <c r="D65" s="623"/>
-      <c r="E65" s="623"/>
-      <c r="F65" s="624"/>
+      <c r="D65" s="624"/>
+      <c r="E65" s="624"/>
+      <c r="F65" s="625"/>
       <c r="G65" s="342">
         <f>SUM(G61:G64)</f>
         <v>0</v>
@@ -65873,12 +65877,12 @@
     <row r="89" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="341"/>
       <c r="B89" s="320"/>
-      <c r="C89" s="622" t="s">
+      <c r="C89" s="623" t="s">
         <v>2372</v>
       </c>
-      <c r="D89" s="623"/>
-      <c r="E89" s="623"/>
-      <c r="F89" s="624"/>
+      <c r="D89" s="624"/>
+      <c r="E89" s="624"/>
+      <c r="F89" s="625"/>
       <c r="G89" s="342">
         <f>SUM(G85:G88)</f>
         <v>0</v>
@@ -65957,12 +65961,12 @@
     <row r="94" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="347"/>
       <c r="B94" s="348"/>
-      <c r="C94" s="622" t="s">
+      <c r="C94" s="623" t="s">
         <v>2372</v>
       </c>
-      <c r="D94" s="623"/>
-      <c r="E94" s="623"/>
-      <c r="F94" s="624"/>
+      <c r="D94" s="624"/>
+      <c r="E94" s="624"/>
+      <c r="F94" s="625"/>
       <c r="G94" s="346">
         <f>SUM(G90:G93)</f>
         <v>0</v>
@@ -66813,7 +66817,7 @@
       <c r="E66" s="10"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C67" s="625" t="s">
+      <c r="C67" s="626" t="s">
         <v>2634</v>
       </c>
       <c r="D67" s="548" t="s">
@@ -66825,7 +66829,7 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C68" s="625"/>
+      <c r="C68" s="626"/>
       <c r="D68" s="548" t="s">
         <v>2362</v>
       </c>
@@ -66835,7 +66839,7 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C69" s="625"/>
+      <c r="C69" s="626"/>
       <c r="D69" s="548" t="s">
         <v>2668</v>
       </c>
@@ -66845,7 +66849,7 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C70" s="625" t="s">
+      <c r="C70" s="626" t="s">
         <v>2669</v>
       </c>
       <c r="D70" s="548" t="s">
@@ -66857,7 +66861,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C71" s="625"/>
+      <c r="C71" s="626"/>
       <c r="D71" s="548" t="s">
         <v>2362</v>
       </c>
@@ -66867,7 +66871,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C72" s="625"/>
+      <c r="C72" s="626"/>
       <c r="D72" s="548" t="s">
         <v>2668</v>
       </c>
@@ -67603,10 +67607,10 @@
       <c r="H5" s="318" t="s">
         <v>2702</v>
       </c>
-      <c r="K5" s="626" t="s">
+      <c r="K5" s="627" t="s">
         <v>2703</v>
       </c>
-      <c r="L5" s="626"/>
+      <c r="L5" s="627"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="309" t="s">
@@ -68237,25 +68241,25 @@
       </c>
     </row>
     <row r="2" spans="2:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="637" t="s">
+      <c r="B2" s="638" t="s">
         <v>2738</v>
       </c>
-      <c r="C2" s="635" t="s">
+      <c r="C2" s="636" t="s">
         <v>2739</v>
       </c>
-      <c r="D2" s="635" t="s">
+      <c r="D2" s="636" t="s">
         <v>2740</v>
       </c>
-      <c r="E2" s="643" t="s">
+      <c r="E2" s="644" t="s">
         <v>2419</v>
       </c>
-      <c r="F2" s="643" t="s">
+      <c r="F2" s="644" t="s">
         <v>2647</v>
       </c>
-      <c r="G2" s="643" t="s">
+      <c r="G2" s="644" t="s">
         <v>2648</v>
       </c>
-      <c r="H2" s="643" t="s">
+      <c r="H2" s="644" t="s">
         <v>2420</v>
       </c>
       <c r="I2" s="438" t="s">
@@ -68273,24 +68277,24 @@
       <c r="M2" s="438" t="s">
         <v>2745</v>
       </c>
-      <c r="N2" s="633" t="s">
+      <c r="N2" s="634" t="s">
         <v>2746</v>
       </c>
-      <c r="O2" s="633" t="s">
+      <c r="O2" s="634" t="s">
         <v>2747</v>
       </c>
-      <c r="P2" s="627" t="s">
+      <c r="P2" s="628" t="s">
         <v>2748</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="B3" s="638"/>
-      <c r="C3" s="636"/>
-      <c r="D3" s="636"/>
-      <c r="E3" s="644"/>
-      <c r="F3" s="644"/>
-      <c r="G3" s="644"/>
-      <c r="H3" s="644"/>
+      <c r="B3" s="639"/>
+      <c r="C3" s="637"/>
+      <c r="D3" s="637"/>
+      <c r="E3" s="645"/>
+      <c r="F3" s="645"/>
+      <c r="G3" s="645"/>
+      <c r="H3" s="645"/>
       <c r="I3" s="439" t="s">
         <v>2749</v>
       </c>
@@ -68298,9 +68302,9 @@
       <c r="K3" s="439"/>
       <c r="L3" s="439"/>
       <c r="M3" s="439"/>
-      <c r="N3" s="634"/>
-      <c r="O3" s="634"/>
-      <c r="P3" s="628"/>
+      <c r="N3" s="635"/>
+      <c r="O3" s="635"/>
+      <c r="P3" s="629"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B4" s="409"/>
@@ -69682,46 +69686,46 @@
       </c>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="639" t="s">
+      <c r="B38" s="640" t="s">
         <v>2738</v>
       </c>
-      <c r="C38" s="641" t="s">
+      <c r="C38" s="642" t="s">
         <v>2623</v>
       </c>
-      <c r="D38" s="641" t="s">
+      <c r="D38" s="642" t="s">
         <v>2758</v>
       </c>
-      <c r="E38" s="641"/>
-      <c r="F38" s="641"/>
-      <c r="G38" s="641"/>
-      <c r="H38" s="641"/>
-      <c r="I38" s="641" t="s">
+      <c r="E38" s="642"/>
+      <c r="F38" s="642"/>
+      <c r="G38" s="642"/>
+      <c r="H38" s="642"/>
+      <c r="I38" s="642" t="s">
         <v>2759</v>
       </c>
-      <c r="J38" s="641"/>
-      <c r="K38" s="641" t="s">
+      <c r="J38" s="642"/>
+      <c r="K38" s="642" t="s">
         <v>2625</v>
       </c>
-      <c r="L38" s="635" t="s">
+      <c r="L38" s="636" t="s">
         <v>2624</v>
       </c>
-      <c r="M38" s="635"/>
-      <c r="N38" s="635"/>
-      <c r="O38" s="647" t="s">
+      <c r="M38" s="636"/>
+      <c r="N38" s="636"/>
+      <c r="O38" s="648" t="s">
         <v>2760</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="640"/>
-      <c r="C39" s="642"/>
-      <c r="D39" s="642"/>
-      <c r="E39" s="642"/>
-      <c r="F39" s="642"/>
-      <c r="G39" s="642"/>
-      <c r="H39" s="642"/>
-      <c r="I39" s="642"/>
-      <c r="J39" s="642"/>
-      <c r="K39" s="642"/>
+      <c r="B39" s="641"/>
+      <c r="C39" s="643"/>
+      <c r="D39" s="643"/>
+      <c r="E39" s="643"/>
+      <c r="F39" s="643"/>
+      <c r="G39" s="643"/>
+      <c r="H39" s="643"/>
+      <c r="I39" s="643"/>
+      <c r="J39" s="643"/>
+      <c r="K39" s="643"/>
       <c r="L39" s="334" t="s">
         <v>503</v>
       </c>
@@ -69731,7 +69735,7 @@
       <c r="N39" s="334" t="s">
         <v>568</v>
       </c>
-      <c r="O39" s="648"/>
+      <c r="O39" s="649"/>
     </row>
     <row r="40" spans="2:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="268">
@@ -69740,17 +69744,17 @@
       <c r="C40" s="269" t="s">
         <v>2629</v>
       </c>
-      <c r="D40" s="631" t="s">
+      <c r="D40" s="632" t="s">
         <v>2761</v>
       </c>
-      <c r="E40" s="631"/>
-      <c r="F40" s="631"/>
-      <c r="G40" s="631"/>
-      <c r="H40" s="631"/>
-      <c r="I40" s="651" t="s">
+      <c r="E40" s="632"/>
+      <c r="F40" s="632"/>
+      <c r="G40" s="632"/>
+      <c r="H40" s="632"/>
+      <c r="I40" s="652" t="s">
         <v>2762</v>
       </c>
-      <c r="J40" s="651"/>
+      <c r="J40" s="652"/>
       <c r="K40" s="270">
         <f>'INCOME STATEMENT'!F6</f>
         <v>61039612496</v>
@@ -69767,7 +69771,7 @@
         <f>'PASAR PEMBANDING'!F22/'PASAR PEMBANDING'!F5</f>
         <v>0.35850278235329225</v>
       </c>
-      <c r="O40" s="645"/>
+      <c r="O40" s="646"/>
     </row>
     <row r="41" spans="2:15" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="271">
@@ -69776,17 +69780,17 @@
       <c r="C41" s="272" t="s">
         <v>2630</v>
       </c>
-      <c r="D41" s="632" t="s">
+      <c r="D41" s="633" t="s">
         <v>2763</v>
       </c>
-      <c r="E41" s="632"/>
-      <c r="F41" s="632"/>
-      <c r="G41" s="632"/>
-      <c r="H41" s="632"/>
-      <c r="I41" s="652" t="s">
+      <c r="E41" s="633"/>
+      <c r="F41" s="633"/>
+      <c r="G41" s="633"/>
+      <c r="H41" s="633"/>
+      <c r="I41" s="653" t="s">
         <v>2762</v>
       </c>
-      <c r="J41" s="652"/>
+      <c r="J41" s="653"/>
       <c r="K41" s="363">
         <f>'BALANCE SHEET'!F49</f>
         <v>29366482204</v>
@@ -69803,7 +69807,7 @@
         <f>'PASAR PEMBANDING'!F22/'PASAR PEMBANDING'!F16</f>
         <v>0.72881454617432406</v>
       </c>
-      <c r="O41" s="646"/>
+      <c r="O41" s="647"/>
     </row>
     <row r="42" spans="2:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="359">
@@ -69813,17 +69817,17 @@
       <c r="C42" s="360" t="s">
         <v>2764</v>
       </c>
-      <c r="D42" s="630" t="s">
+      <c r="D42" s="631" t="s">
         <v>2765</v>
       </c>
-      <c r="E42" s="630"/>
-      <c r="F42" s="630"/>
-      <c r="G42" s="630"/>
-      <c r="H42" s="630"/>
-      <c r="I42" s="650" t="s">
+      <c r="E42" s="631"/>
+      <c r="F42" s="631"/>
+      <c r="G42" s="631"/>
+      <c r="H42" s="631"/>
+      <c r="I42" s="651" t="s">
         <v>2766</v>
       </c>
-      <c r="J42" s="650"/>
+      <c r="J42" s="651"/>
       <c r="K42" s="361">
         <f>'INCOME STATEMENT'!F22</f>
         <v>7333474245</v>
@@ -69840,7 +69844,7 @@
         <f>('PASAR PEMBANDING'!F15+'PASAR PEMBANDING'!F16)/'PASAR PEMBANDING'!F8</f>
         <v>8.0342958423761068</v>
       </c>
-      <c r="O42" s="649" t="s">
+      <c r="O42" s="650" t="s">
         <v>2767</v>
       </c>
     </row>
@@ -69852,17 +69856,17 @@
       <c r="C43" s="269" t="s">
         <v>2768</v>
       </c>
-      <c r="D43" s="631" t="s">
+      <c r="D43" s="632" t="s">
         <v>2769</v>
       </c>
-      <c r="E43" s="631"/>
-      <c r="F43" s="631"/>
-      <c r="G43" s="631"/>
-      <c r="H43" s="631"/>
-      <c r="I43" s="651" t="s">
+      <c r="E43" s="632"/>
+      <c r="F43" s="632"/>
+      <c r="G43" s="632"/>
+      <c r="H43" s="632"/>
+      <c r="I43" s="652" t="s">
         <v>2766</v>
       </c>
-      <c r="J43" s="651"/>
+      <c r="J43" s="652"/>
       <c r="K43" s="270">
         <f>'INCOME STATEMENT'!F18</f>
         <v>7493446732</v>
@@ -69879,7 +69883,7 @@
         <f>('PASAR PEMBANDING'!F15+'PASAR PEMBANDING'!F16)/'PASAR PEMBANDING'!F7</f>
         <v>7.8217264092061214</v>
       </c>
-      <c r="O43" s="645"/>
+      <c r="O43" s="646"/>
     </row>
     <row r="44" spans="2:15" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B44" s="271">
@@ -69889,17 +69893,17 @@
       <c r="C44" s="272" t="s">
         <v>2770</v>
       </c>
-      <c r="D44" s="632" t="s">
+      <c r="D44" s="633" t="s">
         <v>2771</v>
       </c>
-      <c r="E44" s="632"/>
-      <c r="F44" s="632"/>
-      <c r="G44" s="632"/>
-      <c r="H44" s="632"/>
-      <c r="I44" s="652" t="s">
+      <c r="E44" s="633"/>
+      <c r="F44" s="633"/>
+      <c r="G44" s="633"/>
+      <c r="H44" s="633"/>
+      <c r="I44" s="653" t="s">
         <v>2766</v>
       </c>
-      <c r="J44" s="652"/>
+      <c r="J44" s="653"/>
       <c r="K44" s="290">
         <f>K40</f>
         <v>61039612496</v>
@@ -69916,96 +69920,96 @@
         <f>('PASAR PEMBANDING'!F15+'PASAR PEMBANDING'!F16)/'PASAR PEMBANDING'!F5</f>
         <v>0.8218713409123094</v>
       </c>
-      <c r="O44" s="646"/>
+      <c r="O44" s="647"/>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B45" s="225"/>
       <c r="C45" s="225"/>
-      <c r="D45" s="629"/>
-      <c r="E45" s="629"/>
-      <c r="F45" s="629"/>
-      <c r="G45" s="629"/>
-      <c r="H45" s="629"/>
+      <c r="D45" s="630"/>
+      <c r="E45" s="630"/>
+      <c r="F45" s="630"/>
+      <c r="G45" s="630"/>
+      <c r="H45" s="630"/>
       <c r="I45" s="226"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B46" s="225"/>
       <c r="C46" s="225"/>
-      <c r="D46" s="629"/>
-      <c r="E46" s="629"/>
-      <c r="F46" s="629"/>
-      <c r="G46" s="629"/>
-      <c r="H46" s="629"/>
+      <c r="D46" s="630"/>
+      <c r="E46" s="630"/>
+      <c r="F46" s="630"/>
+      <c r="G46" s="630"/>
+      <c r="H46" s="630"/>
       <c r="I46" s="226"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B47" s="225"/>
       <c r="C47" s="225"/>
-      <c r="D47" s="629"/>
-      <c r="E47" s="629"/>
-      <c r="F47" s="629"/>
-      <c r="G47" s="629"/>
-      <c r="H47" s="629"/>
+      <c r="D47" s="630"/>
+      <c r="E47" s="630"/>
+      <c r="F47" s="630"/>
+      <c r="G47" s="630"/>
+      <c r="H47" s="630"/>
       <c r="I47" s="226"/>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B48" s="225"/>
       <c r="C48" s="225"/>
-      <c r="D48" s="629"/>
-      <c r="E48" s="629"/>
-      <c r="F48" s="629"/>
-      <c r="G48" s="629"/>
-      <c r="H48" s="629"/>
+      <c r="D48" s="630"/>
+      <c r="E48" s="630"/>
+      <c r="F48" s="630"/>
+      <c r="G48" s="630"/>
+      <c r="H48" s="630"/>
       <c r="I48" s="226"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49" s="225"/>
       <c r="C49" s="225"/>
-      <c r="D49" s="629"/>
-      <c r="E49" s="629"/>
-      <c r="F49" s="629"/>
-      <c r="G49" s="629"/>
-      <c r="H49" s="629"/>
+      <c r="D49" s="630"/>
+      <c r="E49" s="630"/>
+      <c r="F49" s="630"/>
+      <c r="G49" s="630"/>
+      <c r="H49" s="630"/>
       <c r="I49" s="226"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="225"/>
       <c r="C50" s="225"/>
-      <c r="D50" s="629"/>
-      <c r="E50" s="629"/>
-      <c r="F50" s="629"/>
-      <c r="G50" s="629"/>
-      <c r="H50" s="629"/>
+      <c r="D50" s="630"/>
+      <c r="E50" s="630"/>
+      <c r="F50" s="630"/>
+      <c r="G50" s="630"/>
+      <c r="H50" s="630"/>
       <c r="I50" s="226"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="225"/>
       <c r="C51" s="225"/>
-      <c r="D51" s="629"/>
-      <c r="E51" s="629"/>
-      <c r="F51" s="629"/>
-      <c r="G51" s="629"/>
-      <c r="H51" s="629"/>
+      <c r="D51" s="630"/>
+      <c r="E51" s="630"/>
+      <c r="F51" s="630"/>
+      <c r="G51" s="630"/>
+      <c r="H51" s="630"/>
       <c r="I51" s="226"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="225"/>
       <c r="C52" s="225"/>
-      <c r="D52" s="629"/>
-      <c r="E52" s="629"/>
-      <c r="F52" s="629"/>
-      <c r="G52" s="629"/>
-      <c r="H52" s="629"/>
+      <c r="D52" s="630"/>
+      <c r="E52" s="630"/>
+      <c r="F52" s="630"/>
+      <c r="G52" s="630"/>
+      <c r="H52" s="630"/>
       <c r="I52" s="226"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="225"/>
       <c r="C53" s="225"/>
-      <c r="D53" s="629"/>
-      <c r="E53" s="629"/>
-      <c r="F53" s="629"/>
-      <c r="G53" s="629"/>
-      <c r="H53" s="629"/>
+      <c r="D53" s="630"/>
+      <c r="E53" s="630"/>
+      <c r="F53" s="630"/>
+      <c r="G53" s="630"/>
+      <c r="H53" s="630"/>
       <c r="I53" s="226"/>
     </row>
   </sheetData>
@@ -70119,12 +70123,12 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="570" t="s">
+      <c r="H3" s="571" t="s">
         <v>2220</v>
       </c>
-      <c r="I3" s="570"/>
-      <c r="J3" s="570"/>
-      <c r="K3" s="570"/>
+      <c r="I3" s="571"/>
+      <c r="J3" s="571"/>
+      <c r="K3" s="571"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9" t="s">
         <v>2244</v>
@@ -71189,33 +71193,33 @@
       <c r="C2" s="109"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="614" t="s">
+      <c r="B3" s="615" t="s">
         <v>2772</v>
       </c>
-      <c r="C3" s="614" t="s">
+      <c r="C3" s="615" t="s">
         <v>2602</v>
       </c>
-      <c r="D3" s="617" t="s">
+      <c r="D3" s="618" t="s">
         <v>2773</v>
       </c>
-      <c r="E3" s="617"/>
-      <c r="F3" s="617"/>
-      <c r="G3" s="618"/>
-      <c r="H3" s="616" t="s">
+      <c r="E3" s="618"/>
+      <c r="F3" s="618"/>
+      <c r="G3" s="619"/>
+      <c r="H3" s="617" t="s">
         <v>2604</v>
       </c>
-      <c r="I3" s="617"/>
-      <c r="J3" s="617"/>
-      <c r="K3" s="618"/>
-      <c r="L3" s="616" t="s">
+      <c r="I3" s="618"/>
+      <c r="J3" s="618"/>
+      <c r="K3" s="619"/>
+      <c r="L3" s="617" t="s">
         <v>2605</v>
       </c>
-      <c r="M3" s="617"/>
-      <c r="N3" s="618"/>
+      <c r="M3" s="618"/>
+      <c r="N3" s="619"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="615"/>
-      <c r="C4" s="615"/>
+      <c r="B4" s="616"/>
+      <c r="C4" s="616"/>
       <c r="D4" s="279" t="str">
         <f>'PASAR KESEBANDINGAN'!L39</f>
         <v>CHEM</v>
@@ -71260,7 +71264,7 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="659" t="s">
+      <c r="B5" s="660" t="s">
         <v>2243</v>
       </c>
       <c r="C5" s="231" t="s">
@@ -71288,7 +71292,7 @@
       <c r="N5" s="230"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="660"/>
+      <c r="B6" s="661"/>
       <c r="C6" s="231" t="s">
         <v>2429</v>
       </c>
@@ -71328,7 +71332,7 @@
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="660"/>
+      <c r="B7" s="661"/>
       <c r="C7" s="231" t="s">
         <v>2254</v>
       </c>
@@ -71368,7 +71372,7 @@
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="660"/>
+      <c r="B8" s="661"/>
       <c r="C8" s="231" t="s">
         <v>2257</v>
       </c>
@@ -71408,7 +71412,7 @@
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="661"/>
+      <c r="B9" s="662"/>
       <c r="C9" s="231"/>
       <c r="D9" s="232"/>
       <c r="E9" s="232"/>
@@ -71423,7 +71427,7 @@
       <c r="N9" s="293"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="659" t="s">
+      <c r="B10" s="660" t="s">
         <v>2219</v>
       </c>
       <c r="C10" s="231" t="s">
@@ -71465,7 +71469,7 @@
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="660"/>
+      <c r="B11" s="661"/>
       <c r="C11" s="231" t="s">
         <v>2611</v>
       </c>
@@ -71505,7 +71509,7 @@
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="660"/>
+      <c r="B12" s="661"/>
       <c r="C12" s="231" t="s">
         <v>2612</v>
       </c>
@@ -71534,7 +71538,7 @@
       <c r="N12" s="293"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="660"/>
+      <c r="B13" s="661"/>
       <c r="C13" s="231" t="s">
         <v>2918</v>
       </c>
@@ -71572,7 +71576,7 @@
       <c r="N13" s="293"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="660"/>
+      <c r="B14" s="661"/>
       <c r="C14" s="231" t="s">
         <v>2919</v>
       </c>
@@ -71612,7 +71616,7 @@
       <c r="N14" s="293"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="660"/>
+      <c r="B15" s="661"/>
       <c r="C15" s="231" t="s">
         <v>2615</v>
       </c>
@@ -71641,7 +71645,7 @@
       <c r="N15" s="293"/>
     </row>
     <row r="16" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="660"/>
+      <c r="B16" s="661"/>
       <c r="C16" s="231" t="s">
         <v>2418</v>
       </c>
@@ -71681,7 +71685,7 @@
       <c r="N16" s="293"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B17" s="660"/>
+      <c r="B17" s="661"/>
       <c r="C17" s="231" t="s">
         <v>2774</v>
       </c>
@@ -71695,12 +71699,12 @@
         <v>1435</v>
       </c>
       <c r="G17" s="374"/>
-      <c r="H17" s="663" t="s">
+      <c r="H17" s="664" t="s">
         <v>2775</v>
       </c>
-      <c r="I17" s="663"/>
-      <c r="J17" s="663"/>
-      <c r="K17" s="664"/>
+      <c r="I17" s="664"/>
+      <c r="J17" s="664"/>
+      <c r="K17" s="665"/>
       <c r="L17" s="297">
         <f>SUM(L6:L16)</f>
         <v>1</v>
@@ -71715,7 +71719,7 @@
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B18" s="660"/>
+      <c r="B18" s="661"/>
       <c r="C18" s="231" t="s">
         <v>2920</v>
       </c>
@@ -71740,7 +71744,7 @@
       <c r="N18" s="471"/>
     </row>
     <row r="19" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="660"/>
+      <c r="B19" s="661"/>
       <c r="C19" s="231" t="s">
         <v>2617</v>
       </c>
@@ -71754,12 +71758,12 @@
         <v>800371500</v>
       </c>
       <c r="G19" s="375"/>
-      <c r="H19" s="665" t="s">
+      <c r="H19" s="666" t="s">
         <v>2776</v>
       </c>
-      <c r="I19" s="665"/>
-      <c r="J19" s="665"/>
-      <c r="K19" s="666"/>
+      <c r="I19" s="666"/>
+      <c r="J19" s="666"/>
+      <c r="K19" s="667"/>
       <c r="L19" s="300">
         <f>L17/SUM($L$17:$N$17)</f>
         <v>0.14285714285714285</v>
@@ -71774,7 +71778,7 @@
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B20" s="660"/>
+      <c r="B20" s="661"/>
       <c r="C20" s="231" t="s">
         <v>2618</v>
       </c>
@@ -71796,7 +71800,7 @@
       <c r="N20" s="109"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B21" s="660"/>
+      <c r="B21" s="661"/>
       <c r="C21" s="231" t="s">
         <v>2619</v>
       </c>
@@ -71816,7 +71820,7 @@
       <c r="N21" s="109"/>
     </row>
     <row r="22" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="662"/>
+      <c r="B22" s="663"/>
       <c r="C22" s="235" t="s">
         <v>2777</v>
       </c>
@@ -71851,15 +71855,15 @@
       <c r="C26" s="335" t="s">
         <v>2623</v>
       </c>
-      <c r="D26" s="611" t="s">
+      <c r="D26" s="612" t="s">
         <v>2624</v>
       </c>
-      <c r="E26" s="612"/>
-      <c r="F26" s="613"/>
-      <c r="G26" s="611" t="s">
+      <c r="E26" s="613"/>
+      <c r="F26" s="614"/>
+      <c r="G26" s="612" t="s">
         <v>2625</v>
       </c>
-      <c r="H26" s="613"/>
+      <c r="H26" s="614"/>
       <c r="I26" s="277" t="s">
         <v>2626</v>
       </c>
@@ -71977,24 +71981,24 @@
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G31" s="653">
+      <c r="G31" s="654">
         <f>IF(G30="ENTERPRISE VALUE","DEBT",0)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="654"/>
-      <c r="I31" s="655"/>
+      <c r="H31" s="655"/>
+      <c r="I31" s="656"/>
       <c r="J31" s="378">
         <f>IF(G31="DEBT",('BALANCE SHEET'!F31+'BALANCE SHEET'!F38)*-1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G32" s="656">
+      <c r="G32" s="657">
         <f>IF(G31="DEBT","INDICATED VALUE OF EQUITY",0)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="657"/>
-      <c r="I32" s="658"/>
+      <c r="H32" s="658"/>
+      <c r="I32" s="659"/>
       <c r="J32" s="379">
         <f>IF(G31="DEBT",J30+J31,0)</f>
         <v>0</v>
@@ -72874,11 +72878,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="668" t="s">
+      <c r="B2" s="669" t="s">
         <v>2901</v>
       </c>
-      <c r="C2" s="668"/>
-      <c r="D2" s="668"/>
+      <c r="C2" s="669"/>
+      <c r="D2" s="669"/>
     </row>
     <row r="3" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="333" t="s">
@@ -72929,11 +72933,11 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B8" s="667" t="s">
+      <c r="B8" s="668" t="s">
         <v>2789</v>
       </c>
-      <c r="C8" s="667"/>
-      <c r="D8" s="667"/>
+      <c r="C8" s="668"/>
+      <c r="D8" s="668"/>
     </row>
     <row r="9" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="333" t="s">
@@ -75276,18 +75280,18 @@
       <c r="B10" t="s">
         <v>2306</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>2307</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="38">
         <f>'INCOME STATEMENT'!D35/'BALANCE SHEET'!D27</f>
         <v>0.17125922125784826</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="38">
         <f>'INCOME STATEMENT'!E35/'BALANCE SHEET'!E27</f>
         <v>0.16662309555504853</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="38">
         <f>'INCOME STATEMENT'!F35/'BALANCE SHEET'!F27</f>
         <v>0.17260691642475301</v>
       </c>
@@ -75455,18 +75459,18 @@
       <c r="B19" t="s">
         <v>2318</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>2319</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="38">
         <f>('BALANCE SHEET'!D35+'BALANCE SHEET'!D40)/'BALANCE SHEET'!D27</f>
         <v>0.27430765063832591</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="38">
         <f>('BALANCE SHEET'!E35+'BALANCE SHEET'!E40)/'BALANCE SHEET'!E27</f>
         <v>0.21049859134547844</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="38">
         <f>('BALANCE SHEET'!F35+'BALANCE SHEET'!F40)/'BALANCE SHEET'!F27</f>
         <v>0.12693606429124385</v>
       </c>
@@ -75551,11 +75555,11 @@
       <c r="B23" t="s">
         <v>2326</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="567">
         <f>'BALANCE SHEET'!D49/'BALANCE SHEET'!D27</f>
         <v>0.72569234936167404</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="567">
         <f>'BALANCE SHEET'!E49/'BALANCE SHEET'!E27</f>
         <v>0.78950140865452156</v>
       </c>
@@ -75628,15 +75632,15 @@
       <c r="C27" t="s">
         <v>2331</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="38">
         <f>FCF!C20/'CASH FLOW STATEMENT'!C11</f>
         <v>1.3729913832920679</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="38">
         <f>FCF!D20/'CASH FLOW STATEMENT'!D11</f>
         <v>0.79938136347170852</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="38">
         <f>FCF!E20/'CASH FLOW STATEMENT'!E11</f>
         <v>0.87273791187126881</v>
       </c>

--- a/kka-penilaian-saham.xlsx
+++ b/kka-penilaian-saham.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/persiapantubel/Desktop/claude/superpowers/kka-penilaian-saham/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E307ACFE-F22B-5B4F-A620-34A05E8EE6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15855A9C-FC10-474A-B6B5-1E3BC8F5B6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16500" tabRatio="852" firstSheet="3" activeTab="10" xr2:uid="{9329EE89-472E-4BD7-BEEB-5D8C86697BEE}"/>
+    <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="16500" tabRatio="852" firstSheet="10" activeTab="24" xr2:uid="{9329EE89-472E-4BD7-BEEB-5D8C86697BEE}"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="3" r:id="rId1"/>
@@ -9297,7 +9297,7 @@
     <numFmt numFmtId="184" formatCode="0.000000%"/>
     <numFmt numFmtId="185" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9612,6 +9612,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="38">
@@ -10829,7 +10845,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="670">
+  <cellXfs count="677">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -11654,31 +11670,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
@@ -11695,20 +11699,32 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11728,6 +11744,15 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="73" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="35" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -11742,15 +11767,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="35" borderId="73" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11776,16 +11792,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11812,6 +11828,15 @@
     <xf numFmtId="0" fontId="3" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -11821,20 +11846,71 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="2" fillId="34" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11853,84 +11929,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -11956,12 +11954,39 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -33678,20 +33703,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="568" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="568"/>
-      <c r="C1" s="568"/>
-      <c r="D1" s="568"/>
-      <c r="E1" s="568"/>
+      <c r="A1" s="580" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="580"/>
+      <c r="C1" s="580"/>
+      <c r="D1" s="580"/>
+      <c r="E1" s="580"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="569"/>
-      <c r="B2" s="569"/>
-      <c r="C2" s="569"/>
-      <c r="D2" s="569"/>
-      <c r="E2" s="569"/>
+      <c r="A2" s="581"/>
+      <c r="B2" s="581"/>
+      <c r="C2" s="581"/>
+      <c r="D2" s="581"/>
+      <c r="E2" s="581"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="49" t="s">
@@ -34200,68 +34225,68 @@
       <c r="F1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="572" t="s">
+      <c r="A2" s="578" t="s">
         <v>2350</v>
       </c>
-      <c r="B2" s="572"/>
-      <c r="C2" s="572"/>
-      <c r="D2" s="572"/>
-      <c r="E2" s="572"/>
-      <c r="F2" s="572"/>
+      <c r="B2" s="578"/>
+      <c r="C2" s="578"/>
+      <c r="D2" s="578"/>
+      <c r="E2" s="578"/>
+      <c r="F2" s="578"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E3" s="121"/>
       <c r="F3" s="121"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="573" t="s">
+      <c r="A4" s="572" t="s">
         <v>2351</v>
       </c>
-      <c r="B4" s="573" t="s">
+      <c r="B4" s="572" t="s">
         <v>2352</v>
       </c>
-      <c r="C4" s="573" t="s">
+      <c r="C4" s="572" t="s">
         <v>2353</v>
       </c>
-      <c r="D4" s="574" t="s">
+      <c r="D4" s="568" t="s">
         <v>2354</v>
       </c>
-      <c r="E4" s="573" t="s">
+      <c r="E4" s="572" t="s">
         <v>2355</v>
       </c>
-      <c r="F4" s="573"/>
+      <c r="F4" s="572"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="573"/>
-      <c r="B5" s="573"/>
-      <c r="C5" s="573"/>
-      <c r="D5" s="575"/>
-      <c r="E5" s="573"/>
-      <c r="F5" s="573"/>
+      <c r="A5" s="572"/>
+      <c r="B5" s="572"/>
+      <c r="C5" s="572"/>
+      <c r="D5" s="579"/>
+      <c r="E5" s="572"/>
+      <c r="F5" s="572"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="573"/>
-      <c r="B6" s="573"/>
-      <c r="C6" s="573"/>
-      <c r="D6" s="576"/>
-      <c r="E6" s="573"/>
-      <c r="F6" s="573"/>
+      <c r="A6" s="572"/>
+      <c r="B6" s="572"/>
+      <c r="C6" s="572"/>
+      <c r="D6" s="569"/>
+      <c r="E6" s="572"/>
+      <c r="F6" s="572"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="573">
+      <c r="A7" s="572">
         <v>1</v>
       </c>
-      <c r="B7" s="577" t="s">
+      <c r="B7" s="573" t="s">
         <v>2860</v>
       </c>
-      <c r="C7" s="578" t="s">
+      <c r="C7" s="574" t="s">
         <v>2866</v>
       </c>
       <c r="D7" s="122"/>
-      <c r="E7" s="579" t="s">
+      <c r="E7" s="575" t="s">
         <v>2356</v>
       </c>
-      <c r="F7" s="574">
+      <c r="F7" s="568">
         <f>IF(E7="Ada",0,1)</f>
         <v>1</v>
       </c>
@@ -34285,12 +34310,12 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="573"/>
-      <c r="B8" s="577"/>
-      <c r="C8" s="578"/>
+      <c r="A8" s="572"/>
+      <c r="B8" s="573"/>
+      <c r="C8" s="574"/>
       <c r="D8" s="125"/>
-      <c r="E8" s="580"/>
-      <c r="F8" s="576"/>
+      <c r="E8" s="576"/>
+      <c r="F8" s="569"/>
       <c r="G8" s="124"/>
       <c r="H8" s="124" t="s">
         <v>2356</v>
@@ -34309,20 +34334,20 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="573">
+      <c r="A9" s="572">
         <v>2</v>
       </c>
-      <c r="B9" s="577" t="s">
+      <c r="B9" s="573" t="s">
         <v>2861</v>
       </c>
-      <c r="C9" s="578" t="s">
+      <c r="C9" s="574" t="s">
         <v>2865</v>
       </c>
       <c r="D9" s="122"/>
-      <c r="E9" s="579" t="s">
+      <c r="E9" s="575" t="s">
         <v>2361</v>
       </c>
-      <c r="F9" s="574">
+      <c r="F9" s="568">
         <f>IF(E9="Rendah",0,IF(E9="Sedang",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34344,29 +34369,29 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="573"/>
-      <c r="B10" s="577"/>
-      <c r="C10" s="578"/>
+      <c r="A10" s="572"/>
+      <c r="B10" s="573"/>
+      <c r="C10" s="574"/>
       <c r="D10" s="125"/>
-      <c r="E10" s="580"/>
-      <c r="F10" s="576"/>
+      <c r="E10" s="576"/>
+      <c r="F10" s="569"/>
       <c r="G10" s="124"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="573">
+      <c r="A11" s="572">
         <v>3</v>
       </c>
-      <c r="B11" s="577" t="s">
+      <c r="B11" s="573" t="s">
         <v>2862</v>
       </c>
-      <c r="C11" s="578" t="s">
+      <c r="C11" s="574" t="s">
         <v>2867</v>
       </c>
       <c r="D11" s="122"/>
-      <c r="E11" s="579" t="s">
+      <c r="E11" s="575" t="s">
         <v>2362</v>
       </c>
-      <c r="F11" s="574">
+      <c r="F11" s="568">
         <f>IF(E11="Rendah",0,IF(E11="Moderat",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34375,29 +34400,29 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="573"/>
-      <c r="B12" s="577"/>
-      <c r="C12" s="578"/>
+      <c r="A12" s="572"/>
+      <c r="B12" s="573"/>
+      <c r="C12" s="574"/>
       <c r="D12" s="125"/>
-      <c r="E12" s="580"/>
-      <c r="F12" s="576"/>
+      <c r="E12" s="576"/>
+      <c r="F12" s="569"/>
       <c r="G12" s="124"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="573">
+      <c r="A13" s="572">
         <v>4</v>
       </c>
-      <c r="B13" s="583" t="s">
+      <c r="B13" s="577" t="s">
         <v>2863</v>
       </c>
-      <c r="C13" s="577" t="s">
+      <c r="C13" s="573" t="s">
         <v>2868</v>
       </c>
       <c r="D13" s="126"/>
-      <c r="E13" s="579" t="s">
+      <c r="E13" s="575" t="s">
         <v>2363</v>
       </c>
-      <c r="F13" s="574">
+      <c r="F13" s="568">
         <f>IF(E13="Tidak Ada",0,IF(E13="Sebagian",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34406,29 +34431,29 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="573"/>
-      <c r="B14" s="583"/>
-      <c r="C14" s="577"/>
+      <c r="A14" s="572"/>
+      <c r="B14" s="577"/>
+      <c r="C14" s="573"/>
       <c r="D14" s="127"/>
-      <c r="E14" s="580"/>
-      <c r="F14" s="576"/>
+      <c r="E14" s="576"/>
+      <c r="F14" s="569"/>
       <c r="G14" s="124"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="573">
+      <c r="A15" s="572">
         <v>5</v>
       </c>
-      <c r="B15" s="577" t="s">
+      <c r="B15" s="573" t="s">
         <v>2864</v>
       </c>
-      <c r="C15" s="577" t="s">
+      <c r="C15" s="573" t="s">
         <v>2869</v>
       </c>
       <c r="D15" s="126"/>
-      <c r="E15" s="579" t="s">
+      <c r="E15" s="575" t="s">
         <v>2363</v>
       </c>
-      <c r="F15" s="574">
+      <c r="F15" s="568">
         <f>IF(E15="Tidak",0,IF(E15="Sebagian",0.5,1))</f>
         <v>0.5</v>
       </c>
@@ -34437,21 +34462,21 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="573"/>
-      <c r="B16" s="577"/>
-      <c r="C16" s="577"/>
+      <c r="A16" s="572"/>
+      <c r="B16" s="573"/>
+      <c r="C16" s="573"/>
       <c r="D16" s="127"/>
-      <c r="E16" s="580"/>
-      <c r="F16" s="576"/>
+      <c r="E16" s="576"/>
+      <c r="F16" s="569"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="581" t="s">
+      <c r="A17" s="570" t="s">
         <v>2372</v>
       </c>
-      <c r="B17" s="582"/>
-      <c r="C17" s="582"/>
-      <c r="D17" s="582"/>
-      <c r="E17" s="582"/>
+      <c r="B17" s="571"/>
+      <c r="C17" s="571"/>
+      <c r="D17" s="571"/>
+      <c r="E17" s="571"/>
       <c r="F17" s="130">
         <f>SUM(F7:F16)</f>
         <v>3</v>
@@ -34620,6 +34645,22 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="32">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:F6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A11:A12"/>
@@ -34636,22 +34677,6 @@
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:F6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15:E16" xr:uid="{EDB332F4-870B-4DC3-8B82-E1A61D5A2BB3}">
@@ -34698,68 +34723,68 @@
       <c r="G1" s="121"/>
     </row>
     <row r="2" spans="2:14" ht="19" x14ac:dyDescent="0.25">
-      <c r="B2" s="572" t="s">
+      <c r="B2" s="578" t="s">
         <v>2380</v>
       </c>
-      <c r="C2" s="572"/>
-      <c r="D2" s="572"/>
-      <c r="E2" s="572"/>
-      <c r="F2" s="572"/>
-      <c r="G2" s="572"/>
+      <c r="C2" s="578"/>
+      <c r="D2" s="578"/>
+      <c r="E2" s="578"/>
+      <c r="F2" s="578"/>
+      <c r="G2" s="578"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="F3" s="121"/>
       <c r="G3" s="121"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="573" t="s">
+      <c r="B4" s="572" t="s">
         <v>2351</v>
       </c>
-      <c r="C4" s="573" t="s">
+      <c r="C4" s="572" t="s">
         <v>2352</v>
       </c>
-      <c r="D4" s="573" t="s">
+      <c r="D4" s="572" t="s">
         <v>2381</v>
       </c>
-      <c r="E4" s="574" t="s">
+      <c r="E4" s="568" t="s">
         <v>2354</v>
       </c>
-      <c r="F4" s="573" t="s">
+      <c r="F4" s="572" t="s">
         <v>2382</v>
       </c>
-      <c r="G4" s="573"/>
+      <c r="G4" s="572"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="573"/>
-      <c r="C5" s="573"/>
-      <c r="D5" s="573"/>
-      <c r="E5" s="575"/>
-      <c r="F5" s="573"/>
-      <c r="G5" s="573"/>
+      <c r="B5" s="572"/>
+      <c r="C5" s="572"/>
+      <c r="D5" s="572"/>
+      <c r="E5" s="579"/>
+      <c r="F5" s="572"/>
+      <c r="G5" s="572"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="573"/>
-      <c r="C6" s="573"/>
-      <c r="D6" s="573"/>
-      <c r="E6" s="576"/>
-      <c r="F6" s="573"/>
-      <c r="G6" s="573"/>
+      <c r="B6" s="572"/>
+      <c r="C6" s="572"/>
+      <c r="D6" s="572"/>
+      <c r="E6" s="569"/>
+      <c r="F6" s="572"/>
+      <c r="G6" s="572"/>
     </row>
     <row r="7" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="573">
+      <c r="B7" s="572">
         <v>1</v>
       </c>
-      <c r="C7" s="583" t="s">
+      <c r="C7" s="577" t="s">
         <v>2383</v>
       </c>
-      <c r="D7" s="578" t="s">
+      <c r="D7" s="574" t="s">
         <v>2870</v>
       </c>
       <c r="E7" s="122"/>
-      <c r="F7" s="579" t="s">
+      <c r="F7" s="575" t="s">
         <v>2356</v>
       </c>
-      <c r="G7" s="573">
+      <c r="G7" s="572">
         <f>IF(F7="Ada",0,IF(F7="Terbatas",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34781,12 +34806,12 @@
       <c r="N7" s="124"/>
     </row>
     <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="573"/>
-      <c r="C8" s="583"/>
-      <c r="D8" s="578"/>
+      <c r="B8" s="572"/>
+      <c r="C8" s="577"/>
+      <c r="D8" s="574"/>
       <c r="E8" s="125"/>
-      <c r="F8" s="580"/>
-      <c r="G8" s="573"/>
+      <c r="F8" s="576"/>
+      <c r="G8" s="572"/>
       <c r="I8" s="123" t="s">
         <v>2387</v>
       </c>
@@ -34805,20 +34830,20 @@
       <c r="N8" s="124"/>
     </row>
     <row r="9" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="573">
+      <c r="B9" s="572">
         <v>2</v>
       </c>
-      <c r="C9" s="577" t="s">
+      <c r="C9" s="573" t="s">
         <v>2392</v>
       </c>
-      <c r="D9" s="578" t="s">
+      <c r="D9" s="574" t="s">
         <v>2871</v>
       </c>
       <c r="E9" s="122"/>
-      <c r="F9" s="579" t="s">
+      <c r="F9" s="575" t="s">
         <v>2393</v>
       </c>
-      <c r="G9" s="573">
+      <c r="G9" s="572">
         <f>IF(F9="Tidak Terbatas",0,IF(F9="Segmen Tertentu",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34840,12 +34865,12 @@
       <c r="N9" s="124"/>
     </row>
     <row r="10" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="573"/>
-      <c r="C10" s="577"/>
-      <c r="D10" s="578"/>
+      <c r="B10" s="572"/>
+      <c r="C10" s="573"/>
+      <c r="D10" s="574"/>
       <c r="E10" s="125"/>
-      <c r="F10" s="580"/>
-      <c r="G10" s="573"/>
+      <c r="F10" s="576"/>
+      <c r="G10" s="572"/>
       <c r="I10" s="124"/>
       <c r="J10" s="124"/>
       <c r="K10" s="124"/>
@@ -34854,20 +34879,20 @@
       <c r="N10" s="124"/>
     </row>
     <row r="11" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="573">
+      <c r="B11" s="572">
         <v>3</v>
       </c>
-      <c r="C11" s="583" t="s">
+      <c r="C11" s="577" t="s">
         <v>2396</v>
       </c>
-      <c r="D11" s="578" t="s">
+      <c r="D11" s="574" t="s">
         <v>2872</v>
       </c>
       <c r="E11" s="122"/>
-      <c r="F11" s="579" t="s">
+      <c r="F11" s="575" t="s">
         <v>2356</v>
       </c>
-      <c r="G11" s="573">
+      <c r="G11" s="572">
         <f>IF(F11="Ya",0,IF(F11="Kadang-kadang",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34889,12 +34914,12 @@
       <c r="N11" s="124"/>
     </row>
     <row r="12" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="573"/>
-      <c r="C12" s="583"/>
-      <c r="D12" s="578"/>
+      <c r="B12" s="572"/>
+      <c r="C12" s="577"/>
+      <c r="D12" s="574"/>
       <c r="E12" s="125"/>
-      <c r="F12" s="580"/>
-      <c r="G12" s="573"/>
+      <c r="F12" s="576"/>
+      <c r="G12" s="572"/>
       <c r="I12" s="123" t="s">
         <v>2390</v>
       </c>
@@ -34913,20 +34938,20 @@
       <c r="N12" s="124"/>
     </row>
     <row r="13" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="573">
+      <c r="B13" s="572">
         <v>4</v>
       </c>
-      <c r="C13" s="583" t="s">
+      <c r="C13" s="577" t="s">
         <v>2400</v>
       </c>
-      <c r="D13" s="577" t="s">
+      <c r="D13" s="573" t="s">
         <v>2873</v>
       </c>
       <c r="E13" s="126"/>
-      <c r="F13" s="579" t="s">
+      <c r="F13" s="575" t="s">
         <v>2394</v>
       </c>
-      <c r="G13" s="573">
+      <c r="G13" s="572">
         <f>IF(F13="Diatas",0,IF(F13="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
@@ -34948,183 +34973,183 @@
       <c r="N13" s="124"/>
     </row>
     <row r="14" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="573"/>
-      <c r="C14" s="583"/>
-      <c r="D14" s="577"/>
+      <c r="B14" s="572"/>
+      <c r="C14" s="577"/>
+      <c r="D14" s="573"/>
       <c r="E14" s="127"/>
-      <c r="F14" s="580"/>
-      <c r="G14" s="573"/>
+      <c r="F14" s="576"/>
+      <c r="G14" s="572"/>
     </row>
     <row r="15" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="573">
+      <c r="B15" s="572">
         <v>5</v>
       </c>
-      <c r="C15" s="583" t="s">
+      <c r="C15" s="577" t="s">
         <v>2403</v>
       </c>
-      <c r="D15" s="577" t="s">
+      <c r="D15" s="573" t="s">
         <v>2874</v>
       </c>
       <c r="E15" s="126"/>
-      <c r="F15" s="579" t="s">
+      <c r="F15" s="575" t="s">
         <v>2395</v>
       </c>
-      <c r="G15" s="573">
+      <c r="G15" s="572">
         <f>IF(F15="Tidak, Meningkat",0,IF(F15="Sedang, Stabil",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="573"/>
-      <c r="C16" s="583"/>
-      <c r="D16" s="577"/>
+      <c r="B16" s="572"/>
+      <c r="C16" s="577"/>
+      <c r="D16" s="573"/>
       <c r="E16" s="127"/>
-      <c r="F16" s="580"/>
-      <c r="G16" s="573"/>
+      <c r="F16" s="576"/>
+      <c r="G16" s="572"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="573">
+      <c r="B17" s="572">
         <v>6</v>
       </c>
-      <c r="C17" s="583" t="s">
+      <c r="C17" s="577" t="s">
         <v>2404</v>
       </c>
-      <c r="D17" s="577" t="s">
+      <c r="D17" s="573" t="s">
         <v>2875</v>
       </c>
       <c r="E17" s="126"/>
-      <c r="F17" s="579" t="s">
+      <c r="F17" s="575" t="s">
         <v>2385</v>
       </c>
-      <c r="G17" s="573">
+      <c r="G17" s="572">
         <f>IF(F17="Dibawah",0,IF(F17="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="573"/>
-      <c r="C18" s="583"/>
-      <c r="D18" s="577"/>
+      <c r="B18" s="572"/>
+      <c r="C18" s="577"/>
+      <c r="D18" s="573"/>
       <c r="E18" s="127"/>
-      <c r="F18" s="580"/>
-      <c r="G18" s="573"/>
+      <c r="F18" s="576"/>
+      <c r="G18" s="572"/>
     </row>
     <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="573">
+      <c r="B19" s="572">
         <v>7</v>
       </c>
-      <c r="C19" s="583" t="s">
+      <c r="C19" s="577" t="s">
         <v>2405</v>
       </c>
-      <c r="D19" s="577" t="s">
+      <c r="D19" s="573" t="s">
         <v>2876</v>
       </c>
       <c r="E19" s="126"/>
-      <c r="F19" s="579" t="s">
+      <c r="F19" s="575" t="s">
         <v>2394</v>
       </c>
-      <c r="G19" s="573">
+      <c r="G19" s="572">
         <f>IF(F19="Diatas",0,IF(F19="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="573"/>
-      <c r="C20" s="583"/>
-      <c r="D20" s="577"/>
+      <c r="B20" s="572"/>
+      <c r="C20" s="577"/>
+      <c r="D20" s="573"/>
       <c r="E20" s="127"/>
-      <c r="F20" s="580"/>
-      <c r="G20" s="573"/>
+      <c r="F20" s="576"/>
+      <c r="G20" s="572"/>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="573">
+      <c r="B21" s="572">
         <v>8</v>
       </c>
-      <c r="C21" s="577" t="s">
+      <c r="C21" s="573" t="s">
         <v>2406</v>
       </c>
-      <c r="D21" s="577" t="s">
+      <c r="D21" s="573" t="s">
         <v>2877</v>
       </c>
       <c r="E21" s="126"/>
-      <c r="F21" s="579" t="s">
+      <c r="F21" s="575" t="s">
         <v>2401</v>
       </c>
-      <c r="G21" s="573">
+      <c r="G21" s="572">
         <f>IF(F21="Lebih Besar",0,IF(F21="Rata-rata",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="573"/>
-      <c r="C22" s="577"/>
-      <c r="D22" s="577"/>
+      <c r="B22" s="572"/>
+      <c r="C22" s="573"/>
+      <c r="D22" s="573"/>
       <c r="E22" s="127"/>
-      <c r="F22" s="580"/>
-      <c r="G22" s="573"/>
+      <c r="F22" s="576"/>
+      <c r="G22" s="572"/>
     </row>
     <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="573">
+      <c r="B23" s="572">
         <v>9</v>
       </c>
-      <c r="C23" s="577" t="s">
+      <c r="C23" s="573" t="s">
         <v>2407</v>
       </c>
-      <c r="D23" s="577" t="s">
+      <c r="D23" s="573" t="s">
         <v>2878</v>
       </c>
       <c r="E23" s="126"/>
-      <c r="F23" s="579" t="s">
+      <c r="F23" s="575" t="s">
         <v>2402</v>
       </c>
-      <c r="G23" s="573">
+      <c r="G23" s="572">
         <f>IF(F23="Meningkat",0,IF(F23="Seperti Saat Ini",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="573"/>
-      <c r="C24" s="577"/>
-      <c r="D24" s="577"/>
+      <c r="B24" s="572"/>
+      <c r="C24" s="573"/>
+      <c r="D24" s="573"/>
       <c r="E24" s="127"/>
-      <c r="F24" s="580"/>
-      <c r="G24" s="573"/>
+      <c r="F24" s="576"/>
+      <c r="G24" s="572"/>
     </row>
     <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="573">
+      <c r="B25" s="572">
         <v>10</v>
       </c>
-      <c r="C25" s="583" t="s">
+      <c r="C25" s="577" t="s">
         <v>2408</v>
       </c>
-      <c r="D25" s="584" t="s">
+      <c r="D25" s="585" t="s">
         <v>2879</v>
       </c>
       <c r="E25" s="128"/>
-      <c r="F25" s="579" t="s">
+      <c r="F25" s="575" t="s">
         <v>2360</v>
       </c>
-      <c r="G25" s="573">
+      <c r="G25" s="572">
         <f>IF(F25="Ya",0,IF(F25="Seperti Saat Ini",0.5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="573"/>
-      <c r="C26" s="583"/>
-      <c r="D26" s="584"/>
+      <c r="B26" s="572"/>
+      <c r="C26" s="577"/>
+      <c r="D26" s="585"/>
       <c r="E26" s="129"/>
-      <c r="F26" s="580"/>
-      <c r="G26" s="573"/>
+      <c r="F26" s="576"/>
+      <c r="G26" s="572"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="585" t="s">
+      <c r="B27" s="584" t="s">
         <v>2372</v>
       </c>
-      <c r="C27" s="585"/>
-      <c r="D27" s="585"/>
-      <c r="E27" s="585"/>
-      <c r="F27" s="585"/>
+      <c r="C27" s="584"/>
+      <c r="D27" s="584"/>
+      <c r="E27" s="584"/>
+      <c r="F27" s="584"/>
       <c r="G27" s="130">
         <f>SUM(G7:G26)</f>
         <v>10</v>
@@ -35525,63 +35550,63 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="57">
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:G6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="G25:G26"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:G6"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="F23:F24"/>
   </mergeCells>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F25:F26" xr:uid="{8D06CE09-8DD1-4D3E-B83A-4F637122D459}">
@@ -35636,10 +35661,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="N2" s="570" t="s">
+      <c r="N2" s="582" t="s">
         <v>2414</v>
       </c>
-      <c r="O2" s="570"/>
+      <c r="O2" s="582"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.2">
       <c r="N3" s="501"/>
@@ -35880,26 +35905,26 @@
       <c r="J2" s="486"/>
       <c r="K2" s="486"/>
       <c r="L2" s="487"/>
-      <c r="M2" s="597" t="s">
+      <c r="M2" s="592" t="s">
         <v>2421</v>
       </c>
-      <c r="N2" s="598"/>
-      <c r="O2" s="598"/>
-      <c r="P2" s="598"/>
-      <c r="Q2" s="598"/>
-      <c r="R2" s="598"/>
-      <c r="S2" s="598"/>
-      <c r="T2" s="599"/>
-      <c r="U2" s="597" t="s">
+      <c r="N2" s="593"/>
+      <c r="O2" s="593"/>
+      <c r="P2" s="593"/>
+      <c r="Q2" s="593"/>
+      <c r="R2" s="593"/>
+      <c r="S2" s="593"/>
+      <c r="T2" s="594"/>
+      <c r="U2" s="592" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="598"/>
-      <c r="W2" s="598"/>
-      <c r="X2" s="598"/>
-      <c r="Y2" s="598"/>
-      <c r="Z2" s="598"/>
-      <c r="AA2" s="598"/>
-      <c r="AB2" s="599"/>
+      <c r="V2" s="593"/>
+      <c r="W2" s="593"/>
+      <c r="X2" s="593"/>
+      <c r="Y2" s="593"/>
+      <c r="Z2" s="593"/>
+      <c r="AA2" s="593"/>
+      <c r="AB2" s="594"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B3" s="480"/>
@@ -36642,41 +36667,41 @@
       <c r="G59" s="518" t="s">
         <v>2417</v>
       </c>
-      <c r="H59" s="592">
+      <c r="H59" s="595">
         <f>TL!D11</f>
         <v>4994138866</v>
       </c>
-      <c r="I59" s="593"/>
+      <c r="I59" s="596"/>
       <c r="J59" s="510"/>
       <c r="K59" s="507"/>
       <c r="L59" s="518" t="str">
         <f>TL!H11</f>
         <v>Net Profit</v>
       </c>
-      <c r="M59" s="595">
+      <c r="M59" s="598">
         <f>TL!I11</f>
         <v>0</v>
       </c>
-      <c r="N59" s="596"/>
+      <c r="N59" s="599"/>
       <c r="O59" s="507"/>
       <c r="P59" s="518" t="s">
         <v>2417</v>
       </c>
-      <c r="Q59" s="592">
+      <c r="Q59" s="595">
         <f>TL!M11</f>
         <v>5805826735</v>
       </c>
-      <c r="R59" s="594"/>
+      <c r="R59" s="597"/>
       <c r="S59" s="507"/>
       <c r="T59" s="507"/>
       <c r="U59" s="507" t="s">
         <v>2417</v>
       </c>
-      <c r="V59" s="592">
+      <c r="V59" s="595">
         <f>TL!R11</f>
         <v>135354171907</v>
       </c>
-      <c r="W59" s="592"/>
+      <c r="W59" s="595"/>
       <c r="X59" s="507"/>
       <c r="Y59" s="507"/>
       <c r="Z59" s="507"/>
@@ -36692,41 +36717,41 @@
       <c r="G60" s="518" t="s">
         <v>2418</v>
       </c>
-      <c r="H60" s="592">
+      <c r="H60" s="595">
         <f>TL!D12</f>
         <v>23663464279</v>
       </c>
-      <c r="I60" s="593"/>
+      <c r="I60" s="596"/>
       <c r="J60" s="510"/>
       <c r="K60" s="507"/>
       <c r="L60" s="518" t="str">
         <f>TL!H12</f>
         <v>Ekuitas</v>
       </c>
-      <c r="M60" s="595">
+      <c r="M60" s="598">
         <f>TL!I12</f>
         <v>0</v>
       </c>
-      <c r="N60" s="596"/>
+      <c r="N60" s="599"/>
       <c r="O60" s="507"/>
       <c r="P60" s="518" t="s">
         <v>2418</v>
       </c>
-      <c r="Q60" s="592">
+      <c r="Q60" s="595">
         <f>TL!M12</f>
         <v>29366482204</v>
       </c>
-      <c r="R60" s="594"/>
+      <c r="R60" s="597"/>
       <c r="S60" s="507"/>
       <c r="T60" s="507"/>
       <c r="U60" s="507" t="s">
         <v>2418</v>
       </c>
-      <c r="V60" s="592">
+      <c r="V60" s="595">
         <f>TL!R12</f>
         <v>635570945239</v>
       </c>
-      <c r="W60" s="592"/>
+      <c r="W60" s="595"/>
       <c r="X60" s="507"/>
       <c r="Y60" s="507"/>
       <c r="Z60" s="507"/>
@@ -36893,16 +36918,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="V60:W60"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="M60:N60"/>
     <mergeCell ref="M2:T2"/>
     <mergeCell ref="U2:AB2"/>
     <mergeCell ref="H59:I59"/>
     <mergeCell ref="Q59:R59"/>
     <mergeCell ref="V59:W59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="V60:W60"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="M60:N60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -36953,12 +36978,12 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="571" t="s">
+      <c r="H3" s="583" t="s">
         <v>2220</v>
       </c>
-      <c r="I3" s="571"/>
-      <c r="J3" s="571"/>
-      <c r="K3" s="571"/>
+      <c r="I3" s="583"/>
+      <c r="J3" s="583"/>
+      <c r="K3" s="583"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
     </row>
@@ -59991,18 +60016,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="570" t="s">
+      <c r="A1" s="582" t="s">
         <v>2553</v>
       </c>
-      <c r="B1" s="570"/>
-      <c r="C1" s="570"/>
-      <c r="D1" s="570"/>
-      <c r="E1" s="570"/>
-      <c r="F1" s="570"/>
-      <c r="G1" s="570"/>
-      <c r="H1" s="570"/>
-      <c r="I1" s="570"/>
-      <c r="J1" s="570"/>
+      <c r="B1" s="582"/>
+      <c r="C1" s="582"/>
+      <c r="D1" s="582"/>
+      <c r="E1" s="582"/>
+      <c r="F1" s="582"/>
+      <c r="G1" s="582"/>
+      <c r="H1" s="582"/>
+      <c r="I1" s="582"/>
+      <c r="J1" s="582"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
@@ -61200,12 +61225,12 @@
       <c r="A2" t="s">
         <v>2219</v>
       </c>
-      <c r="H2" s="570" t="s">
+      <c r="H2" s="582" t="s">
         <v>2220</v>
       </c>
-      <c r="I2" s="570"/>
-      <c r="J2" s="570"/>
-      <c r="K2" s="570"/>
+      <c r="I2" s="582"/>
+      <c r="J2" s="582"/>
+      <c r="K2" s="582"/>
       <c r="O2" s="163"/>
       <c r="P2" s="179" t="s">
         <v>2843</v>
@@ -62965,52 +62990,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="608" t="s">
+      <c r="A2" s="610" t="s">
         <v>2582</v>
       </c>
-      <c r="B2" s="608"/>
-      <c r="C2" s="608"/>
-      <c r="D2" s="608"/>
-      <c r="E2" s="608"/>
-      <c r="F2" s="608"/>
-      <c r="G2" s="608"/>
-      <c r="H2" s="608"/>
-      <c r="I2" s="608"/>
-      <c r="J2" s="608"/>
+      <c r="B2" s="610"/>
+      <c r="C2" s="610"/>
+      <c r="D2" s="610"/>
+      <c r="E2" s="610"/>
+      <c r="F2" s="610"/>
+      <c r="G2" s="610"/>
+      <c r="H2" s="610"/>
+      <c r="I2" s="610"/>
+      <c r="J2" s="610"/>
     </row>
     <row r="3" spans="1:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="609" t="str">
+      <c r="A4" s="611" t="str">
         <f>HOME!B4</f>
         <v>PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="B4" s="609"/>
-      <c r="C4" s="609"/>
-      <c r="D4" s="609"/>
-      <c r="E4" s="609"/>
-      <c r="F4" s="609"/>
-      <c r="G4" s="609"/>
-      <c r="H4" s="609"/>
-      <c r="I4" s="609"/>
-      <c r="J4" s="609"/>
+      <c r="B4" s="611"/>
+      <c r="C4" s="611"/>
+      <c r="D4" s="611"/>
+      <c r="E4" s="611"/>
+      <c r="F4" s="611"/>
+      <c r="G4" s="611"/>
+      <c r="H4" s="611"/>
+      <c r="I4" s="611"/>
+      <c r="J4" s="611"/>
     </row>
     <row r="5" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="610" t="str">
+      <c r="A6" s="608" t="str">
         <f>"DATA PENJUALAN "&amp;HOME!B4</f>
         <v>DATA PENJUALAN PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="B6" s="610"/>
-      <c r="C6" s="610"/>
-      <c r="D6" s="610"/>
-      <c r="E6" s="610"/>
-      <c r="G6" s="611" t="str">
+      <c r="B6" s="608"/>
+      <c r="C6" s="608"/>
+      <c r="D6" s="608"/>
+      <c r="E6" s="608"/>
+      <c r="G6" s="609" t="str">
         <f>"GROWTH SALES AND NET INCOME "&amp;HOME!B4</f>
         <v>GROWTH SALES AND NET INCOME PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="H6" s="611"/>
-      <c r="I6" s="611"/>
-      <c r="J6" s="611"/>
+      <c r="H6" s="609"/>
+      <c r="I6" s="609"/>
+      <c r="J6" s="609"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
@@ -63359,35 +63384,35 @@
       <c r="O32" s="56"/>
     </row>
     <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="609" t="s">
+      <c r="A36" s="611" t="s">
         <v>2593</v>
       </c>
-      <c r="B36" s="609"/>
-      <c r="C36" s="609"/>
-      <c r="D36" s="609"/>
-      <c r="E36" s="609"/>
-      <c r="F36" s="609"/>
-      <c r="G36" s="609"/>
-      <c r="H36" s="609"/>
-      <c r="I36" s="609"/>
-      <c r="J36" s="609"/>
+      <c r="B36" s="611"/>
+      <c r="C36" s="611"/>
+      <c r="D36" s="611"/>
+      <c r="E36" s="611"/>
+      <c r="F36" s="611"/>
+      <c r="G36" s="611"/>
+      <c r="H36" s="611"/>
+      <c r="I36" s="611"/>
+      <c r="J36" s="611"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="610" t="str">
+      <c r="A38" s="608" t="str">
         <f>"DATA PENJUALAN/PENDAPATAN INDUSTRI"</f>
         <v>DATA PENJUALAN/PENDAPATAN INDUSTRI</v>
       </c>
-      <c r="B38" s="610"/>
-      <c r="C38" s="610"/>
-      <c r="D38" s="610"/>
-      <c r="E38" s="610"/>
-      <c r="G38" s="611" t="str">
+      <c r="B38" s="608"/>
+      <c r="C38" s="608"/>
+      <c r="D38" s="608"/>
+      <c r="E38" s="608"/>
+      <c r="G38" s="609" t="str">
         <f>"GROWTH INDUSTRI "</f>
         <v xml:space="preserve">GROWTH INDUSTRI </v>
       </c>
-      <c r="H38" s="611"/>
-      <c r="I38" s="611"/>
-      <c r="J38" s="611"/>
+      <c r="H38" s="609"/>
+      <c r="I38" s="609"/>
+      <c r="J38" s="609"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="50" t="s">
@@ -63474,49 +63499,49 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="19" x14ac:dyDescent="0.25">
-      <c r="A58" s="608" t="str">
+      <c r="A58" s="610" t="str">
         <f>A2</f>
         <v>GROWTH</v>
       </c>
-      <c r="B58" s="608"/>
-      <c r="C58" s="608"/>
-      <c r="D58" s="608"/>
-      <c r="E58" s="608"/>
-      <c r="F58" s="608"/>
-      <c r="G58" s="608"/>
-      <c r="H58" s="608"/>
-      <c r="I58" s="608"/>
-      <c r="J58" s="608"/>
+      <c r="B58" s="610"/>
+      <c r="C58" s="610"/>
+      <c r="D58" s="610"/>
+      <c r="E58" s="610"/>
+      <c r="F58" s="610"/>
+      <c r="G58" s="610"/>
+      <c r="H58" s="610"/>
+      <c r="I58" s="610"/>
+      <c r="J58" s="610"/>
     </row>
     <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="609" t="str">
+      <c r="A60" s="611" t="str">
         <f>"PERBANDINGAN GROWTH INDUSTRI DENGAN "&amp;A4</f>
         <v>PERBANDINGAN GROWTH INDUSTRI DENGAN PT RAJA VOLTAMA ELEKTRIK</v>
       </c>
-      <c r="B60" s="609"/>
-      <c r="C60" s="609"/>
-      <c r="D60" s="609"/>
-      <c r="E60" s="609"/>
-      <c r="F60" s="609"/>
-      <c r="G60" s="609"/>
-      <c r="H60" s="609"/>
-      <c r="I60" s="609"/>
-      <c r="J60" s="609"/>
+      <c r="B60" s="611"/>
+      <c r="C60" s="611"/>
+      <c r="D60" s="611"/>
+      <c r="E60" s="611"/>
+      <c r="F60" s="611"/>
+      <c r="G60" s="611"/>
+      <c r="H60" s="611"/>
+      <c r="I60" s="611"/>
+      <c r="J60" s="611"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" s="610" t="s">
+      <c r="A62" s="608" t="s">
         <v>2595</v>
       </c>
-      <c r="B62" s="610"/>
-      <c r="C62" s="610"/>
-      <c r="D62" s="610"/>
-      <c r="E62" s="610"/>
-      <c r="G62" s="611" t="s">
+      <c r="B62" s="608"/>
+      <c r="C62" s="608"/>
+      <c r="D62" s="608"/>
+      <c r="E62" s="608"/>
+      <c r="G62" s="609" t="s">
         <v>2596</v>
       </c>
-      <c r="H62" s="611"/>
-      <c r="I62" s="611"/>
-      <c r="J62" s="611"/>
+      <c r="H62" s="609"/>
+      <c r="I62" s="609"/>
+      <c r="J62" s="609"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="50" t="s">
@@ -63627,21 +63652,21 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A66" s="610" t="str">
+      <c r="A66" s="608" t="str">
         <f>"DATA PENJUALAN/PENDAPATAN INDUSTRI"</f>
         <v>DATA PENJUALAN/PENDAPATAN INDUSTRI</v>
       </c>
-      <c r="B66" s="610"/>
-      <c r="C66" s="610"/>
-      <c r="D66" s="610"/>
-      <c r="E66" s="610"/>
-      <c r="G66" s="611" t="str">
+      <c r="B66" s="608"/>
+      <c r="C66" s="608"/>
+      <c r="D66" s="608"/>
+      <c r="E66" s="608"/>
+      <c r="G66" s="609" t="str">
         <f>"GROWTH INDUSTRI "</f>
         <v xml:space="preserve">GROWTH INDUSTRI </v>
       </c>
-      <c r="H66" s="611"/>
-      <c r="I66" s="611"/>
-      <c r="J66" s="611"/>
+      <c r="H66" s="609"/>
+      <c r="I66" s="609"/>
+      <c r="J66" s="609"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="50" t="s">
@@ -63753,6 +63778,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="G62:J62"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="G66:J66"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="A2:J2"/>
@@ -63760,12 +63791,6 @@
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="G62:J62"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="G66:J66"/>
   </mergeCells>
   <pageMargins left="1.2" right="0.7" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
@@ -64807,28 +64832,28 @@
       <c r="G5" s="227"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="620" t="s">
+      <c r="A6" s="623" t="s">
         <v>2351</v>
       </c>
-      <c r="B6" s="622" t="s">
+      <c r="B6" s="625" t="s">
         <v>2643</v>
       </c>
-      <c r="C6" s="622"/>
-      <c r="D6" s="622"/>
-      <c r="E6" s="622"/>
-      <c r="F6" s="620" t="s">
+      <c r="C6" s="625"/>
+      <c r="D6" s="625"/>
+      <c r="E6" s="625"/>
+      <c r="F6" s="623" t="s">
         <v>2606</v>
       </c>
-      <c r="G6" s="620" t="s">
+      <c r="G6" s="623" t="s">
         <v>2605</v>
       </c>
-      <c r="J6" s="570"/>
-      <c r="K6" s="570"/>
-      <c r="L6" s="570"/>
-      <c r="M6" s="570"/>
+      <c r="J6" s="582"/>
+      <c r="K6" s="582"/>
+      <c r="L6" s="582"/>
+      <c r="M6" s="582"/>
     </row>
     <row r="7" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="621"/>
+      <c r="A7" s="624"/>
       <c r="B7" s="336" t="s">
         <v>2644</v>
       </c>
@@ -64841,8 +64866,8 @@
       <c r="E7" s="336" t="s">
         <v>2604</v>
       </c>
-      <c r="F7" s="621"/>
-      <c r="G7" s="621"/>
+      <c r="F7" s="624"/>
+      <c r="G7" s="624"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="337">
@@ -65125,12 +65150,12 @@
     <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="341"/>
       <c r="B31" s="320"/>
-      <c r="C31" s="623" t="s">
+      <c r="C31" s="620" t="s">
         <v>2372</v>
       </c>
-      <c r="D31" s="624"/>
-      <c r="E31" s="624"/>
-      <c r="F31" s="625"/>
+      <c r="D31" s="621"/>
+      <c r="E31" s="621"/>
+      <c r="F31" s="622"/>
       <c r="G31" s="342">
         <f>SUM(G27:G30)</f>
         <v>0</v>
@@ -65209,12 +65234,12 @@
     <row r="36" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="341"/>
       <c r="B36" s="320"/>
-      <c r="C36" s="623" t="s">
+      <c r="C36" s="620" t="s">
         <v>2372</v>
       </c>
-      <c r="D36" s="624"/>
-      <c r="E36" s="624"/>
-      <c r="F36" s="625"/>
+      <c r="D36" s="621"/>
+      <c r="E36" s="621"/>
+      <c r="F36" s="622"/>
       <c r="G36" s="342">
         <f>SUM(G32:G35)</f>
         <v>0</v>
@@ -65501,12 +65526,12 @@
     <row r="60" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="341"/>
       <c r="B60" s="320"/>
-      <c r="C60" s="623" t="s">
+      <c r="C60" s="620" t="s">
         <v>2372</v>
       </c>
-      <c r="D60" s="624"/>
-      <c r="E60" s="624"/>
-      <c r="F60" s="625"/>
+      <c r="D60" s="621"/>
+      <c r="E60" s="621"/>
+      <c r="F60" s="622"/>
       <c r="G60" s="342">
         <f>SUM(G56:G59)</f>
         <v>0</v>
@@ -65585,12 +65610,12 @@
     <row r="65" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="341"/>
       <c r="B65" s="320"/>
-      <c r="C65" s="623" t="s">
+      <c r="C65" s="620" t="s">
         <v>2372</v>
       </c>
-      <c r="D65" s="624"/>
-      <c r="E65" s="624"/>
-      <c r="F65" s="625"/>
+      <c r="D65" s="621"/>
+      <c r="E65" s="621"/>
+      <c r="F65" s="622"/>
       <c r="G65" s="342">
         <f>SUM(G61:G64)</f>
         <v>0</v>
@@ -65877,12 +65902,12 @@
     <row r="89" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="341"/>
       <c r="B89" s="320"/>
-      <c r="C89" s="623" t="s">
+      <c r="C89" s="620" t="s">
         <v>2372</v>
       </c>
-      <c r="D89" s="624"/>
-      <c r="E89" s="624"/>
-      <c r="F89" s="625"/>
+      <c r="D89" s="621"/>
+      <c r="E89" s="621"/>
+      <c r="F89" s="622"/>
       <c r="G89" s="342">
         <f>SUM(G85:G88)</f>
         <v>0</v>
@@ -65961,12 +65986,12 @@
     <row r="94" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="347"/>
       <c r="B94" s="348"/>
-      <c r="C94" s="623" t="s">
+      <c r="C94" s="620" t="s">
         <v>2372</v>
       </c>
-      <c r="D94" s="624"/>
-      <c r="E94" s="624"/>
-      <c r="F94" s="625"/>
+      <c r="D94" s="621"/>
+      <c r="E94" s="621"/>
+      <c r="F94" s="622"/>
       <c r="G94" s="346">
         <f>SUM(G90:G93)</f>
         <v>0</v>
@@ -66065,17 +66090,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C89:F89"/>
     <mergeCell ref="C94:F94"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C60:F60"/>
     <mergeCell ref="C65:F65"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C89:F89"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -68241,25 +68266,25 @@
       </c>
     </row>
     <row r="2" spans="2:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="638" t="s">
+      <c r="B2" s="642" t="s">
         <v>2738</v>
       </c>
-      <c r="C2" s="636" t="s">
+      <c r="C2" s="633" t="s">
         <v>2739</v>
       </c>
-      <c r="D2" s="636" t="s">
+      <c r="D2" s="633" t="s">
         <v>2740</v>
       </c>
-      <c r="E2" s="644" t="s">
+      <c r="E2" s="646" t="s">
         <v>2419</v>
       </c>
-      <c r="F2" s="644" t="s">
+      <c r="F2" s="646" t="s">
         <v>2647</v>
       </c>
-      <c r="G2" s="644" t="s">
+      <c r="G2" s="646" t="s">
         <v>2648</v>
       </c>
-      <c r="H2" s="644" t="s">
+      <c r="H2" s="646" t="s">
         <v>2420</v>
       </c>
       <c r="I2" s="438" t="s">
@@ -68277,24 +68302,24 @@
       <c r="M2" s="438" t="s">
         <v>2745</v>
       </c>
-      <c r="N2" s="634" t="s">
+      <c r="N2" s="640" t="s">
         <v>2746</v>
       </c>
-      <c r="O2" s="634" t="s">
+      <c r="O2" s="640" t="s">
         <v>2747</v>
       </c>
-      <c r="P2" s="628" t="s">
+      <c r="P2" s="648" t="s">
         <v>2748</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="B3" s="639"/>
-      <c r="C3" s="637"/>
-      <c r="D3" s="637"/>
-      <c r="E3" s="645"/>
-      <c r="F3" s="645"/>
-      <c r="G3" s="645"/>
-      <c r="H3" s="645"/>
+      <c r="B3" s="643"/>
+      <c r="C3" s="634"/>
+      <c r="D3" s="634"/>
+      <c r="E3" s="647"/>
+      <c r="F3" s="647"/>
+      <c r="G3" s="647"/>
+      <c r="H3" s="647"/>
       <c r="I3" s="439" t="s">
         <v>2749</v>
       </c>
@@ -68302,9 +68327,9 @@
       <c r="K3" s="439"/>
       <c r="L3" s="439"/>
       <c r="M3" s="439"/>
-      <c r="N3" s="635"/>
-      <c r="O3" s="635"/>
-      <c r="P3" s="629"/>
+      <c r="N3" s="641"/>
+      <c r="O3" s="641"/>
+      <c r="P3" s="649"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B4" s="409"/>
@@ -69686,46 +69711,46 @@
       </c>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="640" t="s">
+      <c r="B38" s="644" t="s">
         <v>2738</v>
       </c>
-      <c r="C38" s="642" t="s">
+      <c r="C38" s="635" t="s">
         <v>2623</v>
       </c>
-      <c r="D38" s="642" t="s">
+      <c r="D38" s="635" t="s">
         <v>2758</v>
       </c>
-      <c r="E38" s="642"/>
-      <c r="F38" s="642"/>
-      <c r="G38" s="642"/>
-      <c r="H38" s="642"/>
-      <c r="I38" s="642" t="s">
+      <c r="E38" s="635"/>
+      <c r="F38" s="635"/>
+      <c r="G38" s="635"/>
+      <c r="H38" s="635"/>
+      <c r="I38" s="635" t="s">
         <v>2759</v>
       </c>
-      <c r="J38" s="642"/>
-      <c r="K38" s="642" t="s">
+      <c r="J38" s="635"/>
+      <c r="K38" s="635" t="s">
         <v>2625</v>
       </c>
-      <c r="L38" s="636" t="s">
+      <c r="L38" s="633" t="s">
         <v>2624</v>
       </c>
-      <c r="M38" s="636"/>
-      <c r="N38" s="636"/>
-      <c r="O38" s="648" t="s">
+      <c r="M38" s="633"/>
+      <c r="N38" s="633"/>
+      <c r="O38" s="630" t="s">
         <v>2760</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="641"/>
-      <c r="C39" s="643"/>
-      <c r="D39" s="643"/>
-      <c r="E39" s="643"/>
-      <c r="F39" s="643"/>
-      <c r="G39" s="643"/>
-      <c r="H39" s="643"/>
-      <c r="I39" s="643"/>
-      <c r="J39" s="643"/>
-      <c r="K39" s="643"/>
+      <c r="B39" s="645"/>
+      <c r="C39" s="636"/>
+      <c r="D39" s="636"/>
+      <c r="E39" s="636"/>
+      <c r="F39" s="636"/>
+      <c r="G39" s="636"/>
+      <c r="H39" s="636"/>
+      <c r="I39" s="636"/>
+      <c r="J39" s="636"/>
+      <c r="K39" s="636"/>
       <c r="L39" s="334" t="s">
         <v>503</v>
       </c>
@@ -69735,7 +69760,7 @@
       <c r="N39" s="334" t="s">
         <v>568</v>
       </c>
-      <c r="O39" s="649"/>
+      <c r="O39" s="631"/>
     </row>
     <row r="40" spans="2:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="268">
@@ -69744,17 +69769,17 @@
       <c r="C40" s="269" t="s">
         <v>2629</v>
       </c>
-      <c r="D40" s="632" t="s">
+      <c r="D40" s="652" t="s">
         <v>2761</v>
       </c>
-      <c r="E40" s="632"/>
-      <c r="F40" s="632"/>
-      <c r="G40" s="632"/>
-      <c r="H40" s="632"/>
-      <c r="I40" s="652" t="s">
+      <c r="E40" s="652"/>
+      <c r="F40" s="652"/>
+      <c r="G40" s="652"/>
+      <c r="H40" s="652"/>
+      <c r="I40" s="638" t="s">
         <v>2762</v>
       </c>
-      <c r="J40" s="652"/>
+      <c r="J40" s="638"/>
       <c r="K40" s="270">
         <f>'INCOME STATEMENT'!F6</f>
         <v>61039612496</v>
@@ -69771,7 +69796,7 @@
         <f>'PASAR PEMBANDING'!F22/'PASAR PEMBANDING'!F5</f>
         <v>0.35850278235329225</v>
       </c>
-      <c r="O40" s="646"/>
+      <c r="O40" s="628"/>
     </row>
     <row r="41" spans="2:15" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="271">
@@ -69780,17 +69805,17 @@
       <c r="C41" s="272" t="s">
         <v>2630</v>
       </c>
-      <c r="D41" s="633" t="s">
+      <c r="D41" s="653" t="s">
         <v>2763</v>
       </c>
-      <c r="E41" s="633"/>
-      <c r="F41" s="633"/>
-      <c r="G41" s="633"/>
-      <c r="H41" s="633"/>
-      <c r="I41" s="653" t="s">
+      <c r="E41" s="653"/>
+      <c r="F41" s="653"/>
+      <c r="G41" s="653"/>
+      <c r="H41" s="653"/>
+      <c r="I41" s="639" t="s">
         <v>2762</v>
       </c>
-      <c r="J41" s="653"/>
+      <c r="J41" s="639"/>
       <c r="K41" s="363">
         <f>'BALANCE SHEET'!F49</f>
         <v>29366482204</v>
@@ -69807,7 +69832,7 @@
         <f>'PASAR PEMBANDING'!F22/'PASAR PEMBANDING'!F16</f>
         <v>0.72881454617432406</v>
       </c>
-      <c r="O41" s="647"/>
+      <c r="O41" s="629"/>
     </row>
     <row r="42" spans="2:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="359">
@@ -69817,17 +69842,17 @@
       <c r="C42" s="360" t="s">
         <v>2764</v>
       </c>
-      <c r="D42" s="631" t="s">
+      <c r="D42" s="651" t="s">
         <v>2765</v>
       </c>
-      <c r="E42" s="631"/>
-      <c r="F42" s="631"/>
-      <c r="G42" s="631"/>
-      <c r="H42" s="631"/>
-      <c r="I42" s="651" t="s">
+      <c r="E42" s="651"/>
+      <c r="F42" s="651"/>
+      <c r="G42" s="651"/>
+      <c r="H42" s="651"/>
+      <c r="I42" s="637" t="s">
         <v>2766</v>
       </c>
-      <c r="J42" s="651"/>
+      <c r="J42" s="637"/>
       <c r="K42" s="361">
         <f>'INCOME STATEMENT'!F22</f>
         <v>7333474245</v>
@@ -69844,7 +69869,7 @@
         <f>('PASAR PEMBANDING'!F15+'PASAR PEMBANDING'!F16)/'PASAR PEMBANDING'!F8</f>
         <v>8.0342958423761068</v>
       </c>
-      <c r="O42" s="650" t="s">
+      <c r="O42" s="632" t="s">
         <v>2767</v>
       </c>
     </row>
@@ -69856,17 +69881,17 @@
       <c r="C43" s="269" t="s">
         <v>2768</v>
       </c>
-      <c r="D43" s="632" t="s">
+      <c r="D43" s="652" t="s">
         <v>2769</v>
       </c>
-      <c r="E43" s="632"/>
-      <c r="F43" s="632"/>
-      <c r="G43" s="632"/>
-      <c r="H43" s="632"/>
-      <c r="I43" s="652" t="s">
+      <c r="E43" s="652"/>
+      <c r="F43" s="652"/>
+      <c r="G43" s="652"/>
+      <c r="H43" s="652"/>
+      <c r="I43" s="638" t="s">
         <v>2766</v>
       </c>
-      <c r="J43" s="652"/>
+      <c r="J43" s="638"/>
       <c r="K43" s="270">
         <f>'INCOME STATEMENT'!F18</f>
         <v>7493446732</v>
@@ -69883,7 +69908,7 @@
         <f>('PASAR PEMBANDING'!F15+'PASAR PEMBANDING'!F16)/'PASAR PEMBANDING'!F7</f>
         <v>7.8217264092061214</v>
       </c>
-      <c r="O43" s="646"/>
+      <c r="O43" s="628"/>
     </row>
     <row r="44" spans="2:15" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B44" s="271">
@@ -69893,17 +69918,17 @@
       <c r="C44" s="272" t="s">
         <v>2770</v>
       </c>
-      <c r="D44" s="633" t="s">
+      <c r="D44" s="653" t="s">
         <v>2771</v>
       </c>
-      <c r="E44" s="633"/>
-      <c r="F44" s="633"/>
-      <c r="G44" s="633"/>
-      <c r="H44" s="633"/>
-      <c r="I44" s="653" t="s">
+      <c r="E44" s="653"/>
+      <c r="F44" s="653"/>
+      <c r="G44" s="653"/>
+      <c r="H44" s="653"/>
+      <c r="I44" s="639" t="s">
         <v>2766</v>
       </c>
-      <c r="J44" s="653"/>
+      <c r="J44" s="639"/>
       <c r="K44" s="290">
         <f>K40</f>
         <v>61039612496</v>
@@ -69920,122 +69945,100 @@
         <f>('PASAR PEMBANDING'!F15+'PASAR PEMBANDING'!F16)/'PASAR PEMBANDING'!F5</f>
         <v>0.8218713409123094</v>
       </c>
-      <c r="O44" s="647"/>
+      <c r="O44" s="629"/>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B45" s="225"/>
       <c r="C45" s="225"/>
-      <c r="D45" s="630"/>
-      <c r="E45" s="630"/>
-      <c r="F45" s="630"/>
-      <c r="G45" s="630"/>
-      <c r="H45" s="630"/>
+      <c r="D45" s="650"/>
+      <c r="E45" s="650"/>
+      <c r="F45" s="650"/>
+      <c r="G45" s="650"/>
+      <c r="H45" s="650"/>
       <c r="I45" s="226"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B46" s="225"/>
       <c r="C46" s="225"/>
-      <c r="D46" s="630"/>
-      <c r="E46" s="630"/>
-      <c r="F46" s="630"/>
-      <c r="G46" s="630"/>
-      <c r="H46" s="630"/>
+      <c r="D46" s="650"/>
+      <c r="E46" s="650"/>
+      <c r="F46" s="650"/>
+      <c r="G46" s="650"/>
+      <c r="H46" s="650"/>
       <c r="I46" s="226"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B47" s="225"/>
       <c r="C47" s="225"/>
-      <c r="D47" s="630"/>
-      <c r="E47" s="630"/>
-      <c r="F47" s="630"/>
-      <c r="G47" s="630"/>
-      <c r="H47" s="630"/>
+      <c r="D47" s="650"/>
+      <c r="E47" s="650"/>
+      <c r="F47" s="650"/>
+      <c r="G47" s="650"/>
+      <c r="H47" s="650"/>
       <c r="I47" s="226"/>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B48" s="225"/>
       <c r="C48" s="225"/>
-      <c r="D48" s="630"/>
-      <c r="E48" s="630"/>
-      <c r="F48" s="630"/>
-      <c r="G48" s="630"/>
-      <c r="H48" s="630"/>
+      <c r="D48" s="650"/>
+      <c r="E48" s="650"/>
+      <c r="F48" s="650"/>
+      <c r="G48" s="650"/>
+      <c r="H48" s="650"/>
       <c r="I48" s="226"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49" s="225"/>
       <c r="C49" s="225"/>
-      <c r="D49" s="630"/>
-      <c r="E49" s="630"/>
-      <c r="F49" s="630"/>
-      <c r="G49" s="630"/>
-      <c r="H49" s="630"/>
+      <c r="D49" s="650"/>
+      <c r="E49" s="650"/>
+      <c r="F49" s="650"/>
+      <c r="G49" s="650"/>
+      <c r="H49" s="650"/>
       <c r="I49" s="226"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="225"/>
       <c r="C50" s="225"/>
-      <c r="D50" s="630"/>
-      <c r="E50" s="630"/>
-      <c r="F50" s="630"/>
-      <c r="G50" s="630"/>
-      <c r="H50" s="630"/>
+      <c r="D50" s="650"/>
+      <c r="E50" s="650"/>
+      <c r="F50" s="650"/>
+      <c r="G50" s="650"/>
+      <c r="H50" s="650"/>
       <c r="I50" s="226"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="225"/>
       <c r="C51" s="225"/>
-      <c r="D51" s="630"/>
-      <c r="E51" s="630"/>
-      <c r="F51" s="630"/>
-      <c r="G51" s="630"/>
-      <c r="H51" s="630"/>
+      <c r="D51" s="650"/>
+      <c r="E51" s="650"/>
+      <c r="F51" s="650"/>
+      <c r="G51" s="650"/>
+      <c r="H51" s="650"/>
       <c r="I51" s="226"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="225"/>
       <c r="C52" s="225"/>
-      <c r="D52" s="630"/>
-      <c r="E52" s="630"/>
-      <c r="F52" s="630"/>
-      <c r="G52" s="630"/>
-      <c r="H52" s="630"/>
+      <c r="D52" s="650"/>
+      <c r="E52" s="650"/>
+      <c r="F52" s="650"/>
+      <c r="G52" s="650"/>
+      <c r="H52" s="650"/>
       <c r="I52" s="226"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="225"/>
       <c r="C53" s="225"/>
-      <c r="D53" s="630"/>
-      <c r="E53" s="630"/>
-      <c r="F53" s="630"/>
-      <c r="G53" s="630"/>
-      <c r="H53" s="630"/>
+      <c r="D53" s="650"/>
+      <c r="E53" s="650"/>
+      <c r="F53" s="650"/>
+      <c r="G53" s="650"/>
+      <c r="H53" s="650"/>
       <c r="I53" s="226"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="O40:O41"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="O42:O44"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:H39"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="D50:H50"/>
     <mergeCell ref="D51:H51"/>
@@ -70052,6 +70055,28 @@
     <mergeCell ref="D40:H40"/>
     <mergeCell ref="D41:H41"/>
     <mergeCell ref="O2:O3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:H39"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="O40:O41"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="O42:O44"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="N2:N3"/>
   </mergeCells>
   <conditionalFormatting sqref="N5:O6 N25:O29 N7:N24">
     <cfRule type="colorScale" priority="2">
@@ -70095,7 +70120,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" style="543" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.5" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
@@ -70123,12 +70148,12 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="571" t="s">
+      <c r="H3" s="583" t="s">
         <v>2220</v>
       </c>
-      <c r="I3" s="571"/>
-      <c r="J3" s="571"/>
-      <c r="K3" s="571"/>
+      <c r="I3" s="583"/>
+      <c r="J3" s="583"/>
+      <c r="K3" s="583"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9" t="s">
         <v>2244</v>
@@ -70136,7 +70161,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="B5" s="670"/>
       <c r="C5" s="8">
         <f>D5-1</f>
         <v>2018</v>
@@ -70288,7 +70313,7 @@
       <c r="A8" s="2" t="s">
         <v>2247</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="671"/>
       <c r="C8" s="11">
         <f>SUM(C6:C7)</f>
         <v>15248394355</v>
@@ -70326,7 +70351,7 @@
       <c r="M8" s="11"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="672" t="s">
         <v>2248</v>
       </c>
       <c r="C9" s="407">
@@ -70372,7 +70397,7 @@
       <c r="K11" s="94"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="B12" s="543" t="s">
         <v>2250</v>
       </c>
       <c r="C12" s="10">
@@ -70421,7 +70446,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="B13" s="543" t="s">
         <v>2251</v>
       </c>
       <c r="C13" s="10">
@@ -70536,7 +70561,6 @@
       <c r="A16" t="s">
         <v>2823</v>
       </c>
-      <c r="B16" s="543"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
       <c r="J16" s="93"/>
@@ -70544,7 +70568,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="B17" s="673"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -70608,7 +70632,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="672" t="s">
         <v>2255</v>
       </c>
       <c r="C19" s="407"/>
@@ -70630,7 +70654,7 @@
       <c r="K19" s="96"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="1"/>
+      <c r="B20" s="672"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -70644,7 +70668,7 @@
       <c r="A21" s="3" t="s">
         <v>2256</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="673"/>
       <c r="C21" s="14">
         <v>-10356539</v>
       </c>
@@ -70716,7 +70740,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="672" t="s">
         <v>2258</v>
       </c>
       <c r="C23" s="407"/>
@@ -70777,7 +70801,7 @@
       <c r="K25" s="94"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="B26" s="543" t="s">
         <v>2825</v>
       </c>
       <c r="C26" s="10">
@@ -70814,7 +70838,7 @@
       <c r="P26" s="4"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="B27" s="543" t="s">
         <v>2826</v>
       </c>
       <c r="C27" s="10">
@@ -70976,7 +71000,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
+      <c r="B31" s="673"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
@@ -70990,6 +71014,9 @@
       <c r="A32" s="2" t="s">
         <v>2264</v>
       </c>
+      <c r="B32" s="674">
+        <v>0.22</v>
+      </c>
       <c r="C32" s="11">
         <f>+C22+C28+C30</f>
         <v>4798400000</v>
@@ -71043,7 +71070,7 @@
       <c r="A33" t="s">
         <v>2265</v>
       </c>
-      <c r="B33" s="4"/>
+      <c r="B33" s="674"/>
       <c r="C33" s="10">
         <v>-1117701375</v>
       </c>
@@ -71066,7 +71093,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+      <c r="B34" s="673"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
@@ -71080,7 +71107,7 @@
       <c r="A35" s="15" t="s">
         <v>2266</v>
       </c>
-      <c r="B35" s="16"/>
+      <c r="B35" s="675"/>
       <c r="C35" s="17">
         <f>+C32+C33</f>
         <v>3680698625</v>
@@ -71132,7 +71159,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="16"/>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="676" t="s">
         <v>2304</v>
       </c>
       <c r="C36" s="408"/>
@@ -71264,7 +71291,7 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="660" t="s">
+      <c r="B5" s="654" t="s">
         <v>2243</v>
       </c>
       <c r="C5" s="231" t="s">
@@ -71292,7 +71319,7 @@
       <c r="N5" s="230"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="661"/>
+      <c r="B6" s="655"/>
       <c r="C6" s="231" t="s">
         <v>2429</v>
       </c>
@@ -71332,7 +71359,7 @@
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="661"/>
+      <c r="B7" s="655"/>
       <c r="C7" s="231" t="s">
         <v>2254</v>
       </c>
@@ -71372,7 +71399,7 @@
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="661"/>
+      <c r="B8" s="655"/>
       <c r="C8" s="231" t="s">
         <v>2257</v>
       </c>
@@ -71412,7 +71439,7 @@
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="662"/>
+      <c r="B9" s="656"/>
       <c r="C9" s="231"/>
       <c r="D9" s="232"/>
       <c r="E9" s="232"/>
@@ -71427,7 +71454,7 @@
       <c r="N9" s="293"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="660" t="s">
+      <c r="B10" s="654" t="s">
         <v>2219</v>
       </c>
       <c r="C10" s="231" t="s">
@@ -71469,7 +71496,7 @@
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="661"/>
+      <c r="B11" s="655"/>
       <c r="C11" s="231" t="s">
         <v>2611</v>
       </c>
@@ -71509,7 +71536,7 @@
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="661"/>
+      <c r="B12" s="655"/>
       <c r="C12" s="231" t="s">
         <v>2612</v>
       </c>
@@ -71538,7 +71565,7 @@
       <c r="N12" s="293"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="661"/>
+      <c r="B13" s="655"/>
       <c r="C13" s="231" t="s">
         <v>2918</v>
       </c>
@@ -71576,7 +71603,7 @@
       <c r="N13" s="293"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="661"/>
+      <c r="B14" s="655"/>
       <c r="C14" s="231" t="s">
         <v>2919</v>
       </c>
@@ -71616,7 +71643,7 @@
       <c r="N14" s="293"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="661"/>
+      <c r="B15" s="655"/>
       <c r="C15" s="231" t="s">
         <v>2615</v>
       </c>
@@ -71645,7 +71672,7 @@
       <c r="N15" s="293"/>
     </row>
     <row r="16" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="661"/>
+      <c r="B16" s="655"/>
       <c r="C16" s="231" t="s">
         <v>2418</v>
       </c>
@@ -71685,7 +71712,7 @@
       <c r="N16" s="293"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B17" s="661"/>
+      <c r="B17" s="655"/>
       <c r="C17" s="231" t="s">
         <v>2774</v>
       </c>
@@ -71699,12 +71726,12 @@
         <v>1435</v>
       </c>
       <c r="G17" s="374"/>
-      <c r="H17" s="664" t="s">
+      <c r="H17" s="658" t="s">
         <v>2775</v>
       </c>
-      <c r="I17" s="664"/>
-      <c r="J17" s="664"/>
-      <c r="K17" s="665"/>
+      <c r="I17" s="658"/>
+      <c r="J17" s="658"/>
+      <c r="K17" s="659"/>
       <c r="L17" s="297">
         <f>SUM(L6:L16)</f>
         <v>1</v>
@@ -71719,7 +71746,7 @@
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B18" s="661"/>
+      <c r="B18" s="655"/>
       <c r="C18" s="231" t="s">
         <v>2920</v>
       </c>
@@ -71744,7 +71771,7 @@
       <c r="N18" s="471"/>
     </row>
     <row r="19" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="661"/>
+      <c r="B19" s="655"/>
       <c r="C19" s="231" t="s">
         <v>2617</v>
       </c>
@@ -71758,12 +71785,12 @@
         <v>800371500</v>
       </c>
       <c r="G19" s="375"/>
-      <c r="H19" s="666" t="s">
+      <c r="H19" s="660" t="s">
         <v>2776</v>
       </c>
-      <c r="I19" s="666"/>
-      <c r="J19" s="666"/>
-      <c r="K19" s="667"/>
+      <c r="I19" s="660"/>
+      <c r="J19" s="660"/>
+      <c r="K19" s="661"/>
       <c r="L19" s="300">
         <f>L17/SUM($L$17:$N$17)</f>
         <v>0.14285714285714285</v>
@@ -71778,7 +71805,7 @@
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B20" s="661"/>
+      <c r="B20" s="655"/>
       <c r="C20" s="231" t="s">
         <v>2618</v>
       </c>
@@ -71800,7 +71827,7 @@
       <c r="N20" s="109"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B21" s="661"/>
+      <c r="B21" s="655"/>
       <c r="C21" s="231" t="s">
         <v>2619</v>
       </c>
@@ -71820,7 +71847,7 @@
       <c r="N21" s="109"/>
     </row>
     <row r="22" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="663"/>
+      <c r="B22" s="657"/>
       <c r="C22" s="235" t="s">
         <v>2777</v>
       </c>
@@ -71981,24 +72008,24 @@
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="G31" s="654">
+      <c r="G31" s="662">
         <f>IF(G30="ENTERPRISE VALUE","DEBT",0)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="655"/>
-      <c r="I31" s="656"/>
+      <c r="H31" s="663"/>
+      <c r="I31" s="664"/>
       <c r="J31" s="378">
         <f>IF(G31="DEBT",('BALANCE SHEET'!F31+'BALANCE SHEET'!F38)*-1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G32" s="657">
+      <c r="G32" s="665">
         <f>IF(G31="DEBT","INDICATED VALUE OF EQUITY",0)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="658"/>
-      <c r="I32" s="659"/>
+      <c r="H32" s="666"/>
+      <c r="I32" s="667"/>
       <c r="J32" s="379">
         <f>IF(G31="DEBT",J30+J31,0)</f>
         <v>0</v>
@@ -72118,6 +72145,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G32:I32"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B10:B22"/>
@@ -72126,11 +72158,6 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G32:I32"/>
   </mergeCells>
   <conditionalFormatting sqref="G31:G32">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
